--- a/downloads/continente-marcas-2026-10.xlsx
+++ b/downloads/continente-marcas-2026-10.xlsx
@@ -18,12 +18,17 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -69,30 +74,55 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t xml:space="preserve">ref_mfr_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ref_own_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ref_discount_mfr_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cut_mfr_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cut_own_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t xml:space="preserve">promo_own_pct</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">promo_mfr_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">advertised_own_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">advertised_mfr_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">price_index_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t xml:space="preserve">price_cells</t>
         </is>
@@ -120,21 +150,36 @@
         <v>22.2</v>
       </c>
       <c r="I2">
+        <v>29.8</v>
+      </c>
+      <c r="J2">
+        <v>0.0</v>
+      </c>
+      <c r="K2">
+        <v>25.0</v>
+      </c>
+      <c r="L2">
+        <v>5.0</v>
+      </c>
+      <c r="M2">
         <v>14.5</v>
       </c>
-      <c r="J2">
+      <c r="N2">
+        <v>14.5</v>
+      </c>
+      <c r="O2">
         <v>34.8</v>
       </c>
-      <c r="K2">
-        <v>25.0</v>
-      </c>
-      <c r="L2">
-        <v>25.0</v>
-      </c>
-      <c r="M2">
+      <c r="P2">
+        <v>25.0</v>
+      </c>
+      <c r="Q2">
+        <v>25.0</v>
+      </c>
+      <c r="R2">
         <v>56.0</v>
       </c>
-      <c r="N2">
+      <c r="S2">
         <v>209</v>
       </c>
     </row>
@@ -160,18 +205,33 @@
         <v>3.1</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>23.8</v>
       </c>
       <c r="J3">
+        <v>0.0</v>
+      </c>
+      <c r="K3">
+        <v>25.0</v>
+      </c>
+      <c r="L3">
+        <v>1.5</v>
+      </c>
+      <c r="M3">
+        <v>0.0</v>
+      </c>
+      <c r="N3">
+        <v>0.0</v>
+      </c>
+      <c r="O3">
         <v>25.4</v>
       </c>
-      <c r="L3">
-        <v>25.0</v>
-      </c>
-      <c r="M3">
+      <c r="Q3">
+        <v>25.0</v>
+      </c>
+      <c r="R3">
         <v>46.6</v>
       </c>
-      <c r="N3">
+      <c r="S3">
         <v>8</v>
       </c>
     </row>
@@ -197,18 +257,33 @@
         <v>58.2</v>
       </c>
       <c r="I4">
+        <v>2.6</v>
+      </c>
+      <c r="J4">
+        <v>0.0</v>
+      </c>
+      <c r="K4">
+        <v>30.0</v>
+      </c>
+      <c r="L4">
+        <v>12.8</v>
+      </c>
+      <c r="M4">
         <v>21.9</v>
       </c>
-      <c r="J4">
+      <c r="N4">
+        <v>21.9</v>
+      </c>
+      <c r="O4">
         <v>15.4</v>
       </c>
-      <c r="K4">
+      <c r="P4">
         <v>40.0</v>
       </c>
-      <c r="L4">
-        <v>25.0</v>
-      </c>
-      <c r="N4">
+      <c r="Q4">
+        <v>25.0</v>
+      </c>
+      <c r="S4">
         <v>0</v>
       </c>
     </row>
@@ -234,21 +309,36 @@
         <v>18.3</v>
       </c>
       <c r="I5">
+        <v>33.8</v>
+      </c>
+      <c r="J5">
+        <v>0.0</v>
+      </c>
+      <c r="K5">
+        <v>25.0</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
         <v>2.4</v>
       </c>
-      <c r="J5">
+      <c r="N5">
+        <v>2.4</v>
+      </c>
+      <c r="O5">
         <v>34.0</v>
       </c>
-      <c r="K5">
+      <c r="P5">
         <v>10.0</v>
       </c>
-      <c r="L5">
-        <v>25.0</v>
-      </c>
-      <c r="M5">
+      <c r="Q5">
+        <v>25.0</v>
+      </c>
+      <c r="R5">
         <v>53.6</v>
       </c>
-      <c r="N5">
+      <c r="S5">
         <v>52</v>
       </c>
     </row>
@@ -274,21 +364,36 @@
         <v>14.9</v>
       </c>
       <c r="I6">
+        <v>60.8</v>
+      </c>
+      <c r="J6">
+        <v>0.0</v>
+      </c>
+      <c r="K6">
+        <v>30.0</v>
+      </c>
+      <c r="L6">
+        <v>0.3</v>
+      </c>
+      <c r="M6">
         <v>8.3</v>
       </c>
-      <c r="J6">
+      <c r="N6">
+        <v>8.3</v>
+      </c>
+      <c r="O6">
         <v>61.2</v>
       </c>
-      <c r="K6">
+      <c r="P6">
         <v>20.0</v>
       </c>
-      <c r="L6">
+      <c r="Q6">
         <v>30.0</v>
       </c>
-      <c r="M6">
+      <c r="R6">
         <v>40.6</v>
       </c>
-      <c r="N6">
+      <c r="S6">
         <v>32</v>
       </c>
     </row>
@@ -314,21 +419,36 @@
         <v>43.2</v>
       </c>
       <c r="I7">
+        <v>20.5</v>
+      </c>
+      <c r="J7">
+        <v>0.0</v>
+      </c>
+      <c r="K7">
+        <v>20.0</v>
+      </c>
+      <c r="L7">
+        <v>2.0</v>
+      </c>
+      <c r="M7">
         <v>9.0</v>
       </c>
-      <c r="J7">
+      <c r="N7">
+        <v>9.0</v>
+      </c>
+      <c r="O7">
         <v>22.5</v>
       </c>
-      <c r="K7">
+      <c r="P7">
         <v>10.0</v>
       </c>
-      <c r="L7">
+      <c r="Q7">
         <v>20.0</v>
       </c>
-      <c r="M7">
+      <c r="R7">
         <v>70.4</v>
       </c>
-      <c r="N7">
+      <c r="S7">
         <v>53</v>
       </c>
     </row>
@@ -353,13 +473,22 @@
       <c r="H8">
         <v>0.0</v>
       </c>
-      <c r="J8">
+      <c r="I8">
+        <v>6.2</v>
+      </c>
+      <c r="K8">
+        <v>30.0</v>
+      </c>
+      <c r="L8">
+        <v>8.0</v>
+      </c>
+      <c r="O8">
         <v>14.2</v>
       </c>
-      <c r="L8">
+      <c r="Q8">
         <v>30.0</v>
       </c>
-      <c r="N8">
+      <c r="S8">
         <v>0</v>
       </c>
     </row>
@@ -385,21 +514,36 @@
         <v>13.6</v>
       </c>
       <c r="I9">
+        <v>52.7</v>
+      </c>
+      <c r="J9">
+        <v>0.0</v>
+      </c>
+      <c r="K9">
+        <v>25.0</v>
+      </c>
+      <c r="L9">
+        <v>4.8</v>
+      </c>
+      <c r="M9">
         <v>25.3</v>
       </c>
-      <c r="J9">
+      <c r="N9">
+        <v>25.3</v>
+      </c>
+      <c r="O9">
         <v>57.5</v>
       </c>
-      <c r="K9">
+      <c r="P9">
         <v>15.0</v>
       </c>
-      <c r="L9">
-        <v>25.0</v>
-      </c>
-      <c r="M9">
+      <c r="Q9">
+        <v>25.0</v>
+      </c>
+      <c r="R9">
         <v>40.6</v>
       </c>
-      <c r="N9">
+      <c r="S9">
         <v>11</v>
       </c>
     </row>
@@ -425,18 +569,33 @@
         <v>18.6</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>68.0</v>
       </c>
       <c r="J10">
+        <v>0.0</v>
+      </c>
+      <c r="K10">
+        <v>50.0</v>
+      </c>
+      <c r="L10">
+        <v>1.3</v>
+      </c>
+      <c r="M10">
+        <v>0.0</v>
+      </c>
+      <c r="N10">
+        <v>0.0</v>
+      </c>
+      <c r="O10">
         <v>69.3</v>
       </c>
-      <c r="L10">
+      <c r="Q10">
         <v>50.0</v>
       </c>
-      <c r="M10">
+      <c r="R10">
         <v>55.1</v>
       </c>
-      <c r="N10">
+      <c r="S10">
         <v>22</v>
       </c>
     </row>
@@ -462,18 +621,30 @@
         <v>38.6</v>
       </c>
       <c r="I11">
+        <v>0.0</v>
+      </c>
+      <c r="J11">
+        <v>0.0</v>
+      </c>
+      <c r="L11">
+        <v>38.1</v>
+      </c>
+      <c r="M11">
         <v>36.1</v>
       </c>
-      <c r="J11">
+      <c r="N11">
+        <v>36.1</v>
+      </c>
+      <c r="O11">
         <v>38.1</v>
       </c>
-      <c r="K11">
+      <c r="P11">
         <v>20.0</v>
       </c>
-      <c r="L11">
+      <c r="Q11">
         <v>20.0</v>
       </c>
-      <c r="N11">
+      <c r="S11">
         <v>0</v>
       </c>
     </row>
@@ -499,18 +670,33 @@
         <v>21.3</v>
       </c>
       <c r="I12">
+        <v>54.1</v>
+      </c>
+      <c r="J12">
+        <v>0.0</v>
+      </c>
+      <c r="K12">
+        <v>25.0</v>
+      </c>
+      <c r="L12">
+        <v>0.0</v>
+      </c>
+      <c r="M12">
         <v>0.4</v>
       </c>
-      <c r="J12">
+      <c r="N12">
+        <v>0.4</v>
+      </c>
+      <c r="O12">
         <v>54.1</v>
       </c>
-      <c r="L12">
-        <v>25.0</v>
-      </c>
-      <c r="M12">
+      <c r="Q12">
+        <v>25.0</v>
+      </c>
+      <c r="R12">
         <v>61.4</v>
       </c>
-      <c r="N12">
+      <c r="S12">
         <v>14</v>
       </c>
     </row>
@@ -536,18 +722,33 @@
         <v>6.9</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>14.1</v>
       </c>
       <c r="J13">
+        <v>0.0</v>
+      </c>
+      <c r="K13">
+        <v>30.0</v>
+      </c>
+      <c r="L13">
+        <v>13.7</v>
+      </c>
+      <c r="M13">
+        <v>0.0</v>
+      </c>
+      <c r="N13">
+        <v>0.0</v>
+      </c>
+      <c r="O13">
         <v>27.8</v>
       </c>
-      <c r="L13">
+      <c r="Q13">
         <v>20.0</v>
       </c>
-      <c r="M13">
+      <c r="R13">
         <v>60.0</v>
       </c>
-      <c r="N13">
+      <c r="S13">
         <v>5</v>
       </c>
     </row>
@@ -573,18 +774,33 @@
         <v>38.8</v>
       </c>
       <c r="I14">
+        <v>47.3</v>
+      </c>
+      <c r="J14">
+        <v>0.0</v>
+      </c>
+      <c r="K14">
+        <v>30.0</v>
+      </c>
+      <c r="L14">
+        <v>0.0</v>
+      </c>
+      <c r="M14">
         <v>1.0</v>
       </c>
-      <c r="J14">
+      <c r="N14">
+        <v>1.0</v>
+      </c>
+      <c r="O14">
         <v>47.3</v>
       </c>
-      <c r="L14">
+      <c r="Q14">
         <v>30.0</v>
       </c>
-      <c r="M14">
+      <c r="R14">
         <v>56.8</v>
       </c>
-      <c r="N14">
+      <c r="S14">
         <v>12</v>
       </c>
     </row>
@@ -609,13 +825,22 @@
       <c r="H15">
         <v>0.0</v>
       </c>
-      <c r="J15">
+      <c r="I15">
+        <v>1.9</v>
+      </c>
+      <c r="K15">
+        <v>20.0</v>
+      </c>
+      <c r="L15">
+        <v>19.7</v>
+      </c>
+      <c r="O15">
         <v>21.6</v>
       </c>
-      <c r="L15">
-        <v>25.0</v>
-      </c>
-      <c r="N15">
+      <c r="Q15">
+        <v>25.0</v>
+      </c>
+      <c r="S15">
         <v>0</v>
       </c>
     </row>
@@ -640,13 +865,22 @@
       <c r="H16">
         <v>4.5</v>
       </c>
-      <c r="J16">
+      <c r="I16">
+        <v>16.2</v>
+      </c>
+      <c r="K16">
+        <v>15.0</v>
+      </c>
+      <c r="L16">
+        <v>0.7</v>
+      </c>
+      <c r="O16">
         <v>16.8</v>
       </c>
-      <c r="L16">
+      <c r="Q16">
         <v>15.0</v>
       </c>
-      <c r="N16">
+      <c r="S16">
         <v>0</v>
       </c>
     </row>
@@ -671,16 +905,25 @@
       <c r="H17">
         <v>14.7</v>
       </c>
-      <c r="J17">
+      <c r="I17">
+        <v>19.2</v>
+      </c>
+      <c r="K17">
+        <v>25.0</v>
+      </c>
+      <c r="L17">
+        <v>10.1</v>
+      </c>
+      <c r="O17">
         <v>29.3</v>
       </c>
-      <c r="K17">
-        <v>25.0</v>
-      </c>
-      <c r="L17">
-        <v>25.0</v>
-      </c>
-      <c r="N17">
+      <c r="P17">
+        <v>25.0</v>
+      </c>
+      <c r="Q17">
+        <v>25.0</v>
+      </c>
+      <c r="S17">
         <v>0</v>
       </c>
     </row>
@@ -710,13 +953,22 @@
       <c r="H18">
         <v>0.2</v>
       </c>
-      <c r="J18">
+      <c r="I18">
+        <v>22.7</v>
+      </c>
+      <c r="K18">
+        <v>25.0</v>
+      </c>
+      <c r="L18">
+        <v>2.1</v>
+      </c>
+      <c r="O18">
         <v>24.8</v>
       </c>
-      <c r="L18">
-        <v>25.0</v>
-      </c>
-      <c r="N18">
+      <c r="Q18">
+        <v>25.0</v>
+      </c>
+      <c r="S18">
         <v>0</v>
       </c>
     </row>
@@ -747,18 +999,33 @@
         <v>65.7</v>
       </c>
       <c r="I19">
+        <v>2.4</v>
+      </c>
+      <c r="J19">
+        <v>0.0</v>
+      </c>
+      <c r="K19">
+        <v>35.0</v>
+      </c>
+      <c r="L19">
+        <v>3.3</v>
+      </c>
+      <c r="M19">
         <v>12.6</v>
       </c>
-      <c r="J19">
+      <c r="N19">
+        <v>12.6</v>
+      </c>
+      <c r="O19">
         <v>5.7</v>
       </c>
-      <c r="K19">
+      <c r="P19">
         <v>40.0</v>
       </c>
-      <c r="L19">
+      <c r="Q19">
         <v>30.0</v>
       </c>
-      <c r="N19">
+      <c r="S19">
         <v>0</v>
       </c>
     </row>
@@ -789,18 +1056,33 @@
         <v>11.9</v>
       </c>
       <c r="I20">
+        <v>68.0</v>
+      </c>
+      <c r="J20">
+        <v>0.0</v>
+      </c>
+      <c r="K20">
+        <v>30.0</v>
+      </c>
+      <c r="L20">
+        <v>0.4</v>
+      </c>
+      <c r="M20">
         <v>0.8</v>
       </c>
-      <c r="J20">
+      <c r="N20">
+        <v>0.8</v>
+      </c>
+      <c r="O20">
         <v>68.4</v>
       </c>
-      <c r="L20">
+      <c r="Q20">
         <v>30.0</v>
       </c>
-      <c r="M20">
+      <c r="R20">
         <v>43.1</v>
       </c>
-      <c r="N20">
+      <c r="S20">
         <v>4</v>
       </c>
     </row>
@@ -831,21 +1113,36 @@
         <v>11.6</v>
       </c>
       <c r="I21">
+        <v>50.1</v>
+      </c>
+      <c r="J21">
+        <v>0.0</v>
+      </c>
+      <c r="K21">
+        <v>25.0</v>
+      </c>
+      <c r="L21">
+        <v>6.6</v>
+      </c>
+      <c r="M21">
         <v>25.8</v>
       </c>
-      <c r="J21">
+      <c r="N21">
+        <v>25.8</v>
+      </c>
+      <c r="O21">
         <v>56.7</v>
       </c>
-      <c r="K21">
+      <c r="P21">
         <v>15.0</v>
       </c>
-      <c r="L21">
-        <v>25.0</v>
-      </c>
-      <c r="M21">
+      <c r="Q21">
+        <v>25.0</v>
+      </c>
+      <c r="R21">
         <v>33.1</v>
       </c>
-      <c r="N21">
+      <c r="S21">
         <v>5</v>
       </c>
     </row>
@@ -876,21 +1173,36 @@
         <v>14.4</v>
       </c>
       <c r="I22">
+        <v>53.5</v>
+      </c>
+      <c r="J22">
+        <v>0.0</v>
+      </c>
+      <c r="K22">
+        <v>25.0</v>
+      </c>
+      <c r="L22">
+        <v>3.2</v>
+      </c>
+      <c r="M22">
         <v>29.5</v>
       </c>
-      <c r="J22">
+      <c r="N22">
+        <v>29.5</v>
+      </c>
+      <c r="O22">
         <v>56.7</v>
       </c>
-      <c r="K22">
+      <c r="P22">
         <v>10.0</v>
       </c>
-      <c r="L22">
-        <v>25.0</v>
-      </c>
-      <c r="M22">
+      <c r="Q22">
+        <v>25.0</v>
+      </c>
+      <c r="R22">
         <v>46.7</v>
       </c>
-      <c r="N22">
+      <c r="S22">
         <v>4</v>
       </c>
     </row>
@@ -921,18 +1233,33 @@
         <v>15.5</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>57.6</v>
       </c>
       <c r="J23">
+        <v>0.0</v>
+      </c>
+      <c r="K23">
+        <v>35.0</v>
+      </c>
+      <c r="L23">
+        <v>1.3</v>
+      </c>
+      <c r="M23">
+        <v>0.0</v>
+      </c>
+      <c r="N23">
+        <v>0.0</v>
+      </c>
+      <c r="O23">
         <v>58.8</v>
       </c>
-      <c r="L23">
+      <c r="Q23">
         <v>35.0</v>
       </c>
-      <c r="M23">
+      <c r="R23">
         <v>48.2</v>
       </c>
-      <c r="N23">
+      <c r="S23">
         <v>8</v>
       </c>
     </row>
@@ -963,21 +1290,36 @@
         <v>16.0</v>
       </c>
       <c r="I24">
+        <v>27.2</v>
+      </c>
+      <c r="J24">
+        <v>0.0</v>
+      </c>
+      <c r="K24">
+        <v>15.0</v>
+      </c>
+      <c r="L24">
+        <v>0.8</v>
+      </c>
+      <c r="M24">
         <v>11.7</v>
       </c>
-      <c r="J24">
+      <c r="N24">
+        <v>11.7</v>
+      </c>
+      <c r="O24">
         <v>28.0</v>
       </c>
-      <c r="K24">
+      <c r="P24">
         <v>10.0</v>
       </c>
-      <c r="L24">
+      <c r="Q24">
         <v>15.0</v>
       </c>
-      <c r="M24">
+      <c r="R24">
         <v>74.8</v>
       </c>
-      <c r="N24">
+      <c r="S24">
         <v>8</v>
       </c>
     </row>
@@ -1007,13 +1349,22 @@
       <c r="H25">
         <v>0.9</v>
       </c>
-      <c r="J25">
+      <c r="I25">
+        <v>13.6</v>
+      </c>
+      <c r="K25">
+        <v>20.0</v>
+      </c>
+      <c r="L25">
+        <v>0.1</v>
+      </c>
+      <c r="O25">
         <v>13.7</v>
       </c>
-      <c r="L25">
+      <c r="Q25">
         <v>20.0</v>
       </c>
-      <c r="N25">
+      <c r="S25">
         <v>0</v>
       </c>
     </row>
@@ -1043,13 +1394,22 @@
       <c r="H26">
         <v>0.0</v>
       </c>
-      <c r="J26">
+      <c r="I26">
         <v>8.5</v>
       </c>
+      <c r="K26">
+        <v>25.0</v>
+      </c>
       <c r="L26">
-        <v>25.0</v>
-      </c>
-      <c r="N26">
+        <v>0.0</v>
+      </c>
+      <c r="O26">
+        <v>8.5</v>
+      </c>
+      <c r="Q26">
+        <v>25.0</v>
+      </c>
+      <c r="S26">
         <v>0</v>
       </c>
     </row>
@@ -1080,18 +1440,33 @@
         <v>16.7</v>
       </c>
       <c r="I27">
+        <v>25.4</v>
+      </c>
+      <c r="J27">
+        <v>0.0</v>
+      </c>
+      <c r="K27">
+        <v>25.0</v>
+      </c>
+      <c r="L27">
+        <v>0.2</v>
+      </c>
+      <c r="M27">
         <v>4.6</v>
       </c>
-      <c r="J27">
+      <c r="N27">
+        <v>4.6</v>
+      </c>
+      <c r="O27">
         <v>25.6</v>
       </c>
-      <c r="L27">
-        <v>25.0</v>
-      </c>
-      <c r="M27">
+      <c r="Q27">
+        <v>25.0</v>
+      </c>
+      <c r="R27">
         <v>47.9</v>
       </c>
-      <c r="N27">
+      <c r="S27">
         <v>7</v>
       </c>
     </row>
@@ -1121,13 +1496,22 @@
       <c r="H28">
         <v>0.0</v>
       </c>
-      <c r="J28">
+      <c r="I28">
         <v>7.8</v>
       </c>
+      <c r="K28">
+        <v>35.0</v>
+      </c>
       <c r="L28">
+        <v>0.0</v>
+      </c>
+      <c r="O28">
+        <v>7.8</v>
+      </c>
+      <c r="Q28">
         <v>35.0</v>
       </c>
-      <c r="N28">
+      <c r="S28">
         <v>0</v>
       </c>
     </row>
@@ -1158,18 +1542,33 @@
         <v>23.6</v>
       </c>
       <c r="I29">
+        <v>12.4</v>
+      </c>
+      <c r="J29">
+        <v>0.0</v>
+      </c>
+      <c r="K29">
+        <v>20.0</v>
+      </c>
+      <c r="L29">
+        <v>2.7</v>
+      </c>
+      <c r="M29">
         <v>2.0</v>
       </c>
-      <c r="J29">
+      <c r="N29">
+        <v>2.0</v>
+      </c>
+      <c r="O29">
         <v>15.1</v>
       </c>
-      <c r="L29">
+      <c r="Q29">
         <v>20.0</v>
       </c>
-      <c r="M29">
+      <c r="R29">
         <v>68.7</v>
       </c>
-      <c r="N29">
+      <c r="S29">
         <v>8</v>
       </c>
     </row>
@@ -1200,18 +1599,33 @@
         <v>10.4</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>24.3</v>
       </c>
       <c r="J30">
+        <v>0.0</v>
+      </c>
+      <c r="K30">
+        <v>25.0</v>
+      </c>
+      <c r="L30">
+        <v>0.0</v>
+      </c>
+      <c r="M30">
+        <v>0.0</v>
+      </c>
+      <c r="N30">
+        <v>0.0</v>
+      </c>
+      <c r="O30">
         <v>24.3</v>
       </c>
-      <c r="L30">
-        <v>25.0</v>
-      </c>
-      <c r="M30">
+      <c r="Q30">
+        <v>25.0</v>
+      </c>
+      <c r="R30">
         <v>44.6</v>
       </c>
-      <c r="N30">
+      <c r="S30">
         <v>4</v>
       </c>
     </row>
@@ -1242,18 +1656,33 @@
         <v>19.3</v>
       </c>
       <c r="I31">
+        <v>25.7</v>
+      </c>
+      <c r="J31">
+        <v>0.0</v>
+      </c>
+      <c r="K31">
+        <v>30.0</v>
+      </c>
+      <c r="L31">
+        <v>0.0</v>
+      </c>
+      <c r="M31">
         <v>15.7</v>
       </c>
-      <c r="J31">
+      <c r="N31">
+        <v>15.7</v>
+      </c>
+      <c r="O31">
         <v>25.7</v>
       </c>
-      <c r="K31">
+      <c r="P31">
         <v>20.0</v>
       </c>
-      <c r="L31">
+      <c r="Q31">
         <v>30.0</v>
       </c>
-      <c r="N31">
+      <c r="S31">
         <v>0</v>
       </c>
     </row>
@@ -1284,18 +1713,33 @@
         <v>21.8</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>67.4</v>
       </c>
       <c r="J32">
+        <v>0.0</v>
+      </c>
+      <c r="K32">
+        <v>25.0</v>
+      </c>
+      <c r="L32">
+        <v>0.0</v>
+      </c>
+      <c r="M32">
+        <v>0.0</v>
+      </c>
+      <c r="N32">
+        <v>0.0</v>
+      </c>
+      <c r="O32">
         <v>67.4</v>
       </c>
-      <c r="L32">
-        <v>25.0</v>
-      </c>
-      <c r="M32">
+      <c r="Q32">
+        <v>25.0</v>
+      </c>
+      <c r="R32">
         <v>59.8</v>
       </c>
-      <c r="N32">
+      <c r="S32">
         <v>9</v>
       </c>
     </row>
@@ -1326,18 +1770,33 @@
         <v>19.3</v>
       </c>
       <c r="I33">
+        <v>44.4</v>
+      </c>
+      <c r="J33">
+        <v>0.0</v>
+      </c>
+      <c r="K33">
+        <v>25.0</v>
+      </c>
+      <c r="L33">
+        <v>0.0</v>
+      </c>
+      <c r="M33">
         <v>2.6</v>
       </c>
-      <c r="J33">
+      <c r="N33">
+        <v>2.6</v>
+      </c>
+      <c r="O33">
         <v>44.4</v>
       </c>
-      <c r="L33">
-        <v>25.0</v>
-      </c>
-      <c r="M33">
+      <c r="Q33">
+        <v>25.0</v>
+      </c>
+      <c r="R33">
         <v>37.7</v>
       </c>
-      <c r="N33">
+      <c r="S33">
         <v>7</v>
       </c>
     </row>
@@ -1368,18 +1827,33 @@
         <v>14.6</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>36.7</v>
       </c>
       <c r="J34">
+        <v>0.0</v>
+      </c>
+      <c r="K34">
+        <v>25.0</v>
+      </c>
+      <c r="L34">
+        <v>0.0</v>
+      </c>
+      <c r="M34">
+        <v>0.0</v>
+      </c>
+      <c r="N34">
+        <v>0.0</v>
+      </c>
+      <c r="O34">
         <v>36.7</v>
       </c>
-      <c r="L34">
-        <v>25.0</v>
-      </c>
-      <c r="M34">
+      <c r="Q34">
+        <v>25.0</v>
+      </c>
+      <c r="R34">
         <v>60.8</v>
       </c>
-      <c r="N34">
+      <c r="S34">
         <v>3</v>
       </c>
     </row>
@@ -1410,18 +1884,33 @@
         <v>18.8</v>
       </c>
       <c r="I35">
+        <v>37.8</v>
+      </c>
+      <c r="J35">
+        <v>0.0</v>
+      </c>
+      <c r="K35">
+        <v>25.0</v>
+      </c>
+      <c r="L35">
+        <v>0.0</v>
+      </c>
+      <c r="M35">
         <v>2.8</v>
       </c>
-      <c r="J35">
+      <c r="N35">
+        <v>2.8</v>
+      </c>
+      <c r="O35">
         <v>37.8</v>
       </c>
-      <c r="L35">
-        <v>25.0</v>
-      </c>
-      <c r="M35">
+      <c r="Q35">
+        <v>25.0</v>
+      </c>
+      <c r="R35">
         <v>59.4</v>
       </c>
-      <c r="N35">
+      <c r="S35">
         <v>5</v>
       </c>
     </row>
@@ -1452,18 +1941,33 @@
         <v>28.1</v>
       </c>
       <c r="I36">
-        <v>0.0</v>
+        <v>30.7</v>
       </c>
       <c r="J36">
+        <v>0.0</v>
+      </c>
+      <c r="K36">
+        <v>20.0</v>
+      </c>
+      <c r="L36">
+        <v>0.0</v>
+      </c>
+      <c r="M36">
+        <v>0.0</v>
+      </c>
+      <c r="N36">
+        <v>0.0</v>
+      </c>
+      <c r="O36">
         <v>30.7</v>
       </c>
-      <c r="L36">
+      <c r="Q36">
         <v>20.0</v>
       </c>
-      <c r="M36">
+      <c r="R36">
         <v>44.2</v>
       </c>
-      <c r="N36">
+      <c r="S36">
         <v>6</v>
       </c>
     </row>
@@ -1494,18 +1998,33 @@
         <v>14.0</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>91.4</v>
       </c>
       <c r="J37">
+        <v>0.0</v>
+      </c>
+      <c r="K37">
+        <v>50.0</v>
+      </c>
+      <c r="L37">
+        <v>0.0</v>
+      </c>
+      <c r="M37">
+        <v>0.0</v>
+      </c>
+      <c r="N37">
+        <v>0.0</v>
+      </c>
+      <c r="O37">
         <v>91.4</v>
       </c>
-      <c r="L37">
+      <c r="Q37">
         <v>50.0</v>
       </c>
-      <c r="M37">
+      <c r="R37">
         <v>65.4</v>
       </c>
-      <c r="N37">
+      <c r="S37">
         <v>4</v>
       </c>
     </row>
@@ -1536,15 +2055,30 @@
         <v>64.2</v>
       </c>
       <c r="I38">
+        <v>11.8</v>
+      </c>
+      <c r="J38">
+        <v>0.0</v>
+      </c>
+      <c r="K38">
+        <v>30.0</v>
+      </c>
+      <c r="L38">
+        <v>1.1</v>
+      </c>
+      <c r="M38">
         <v>2.7</v>
       </c>
-      <c r="J38">
+      <c r="N38">
+        <v>2.7</v>
+      </c>
+      <c r="O38">
         <v>12.8</v>
       </c>
-      <c r="L38">
+      <c r="Q38">
         <v>30.0</v>
       </c>
-      <c r="N38">
+      <c r="S38">
         <v>0</v>
       </c>
     </row>
@@ -1575,15 +2109,27 @@
         <v>79.2</v>
       </c>
       <c r="I39">
+        <v>0.0</v>
+      </c>
+      <c r="J39">
+        <v>0.0</v>
+      </c>
+      <c r="L39">
+        <v>1.8</v>
+      </c>
+      <c r="M39">
         <v>26.8</v>
       </c>
-      <c r="J39">
+      <c r="N39">
+        <v>26.8</v>
+      </c>
+      <c r="O39">
         <v>1.8</v>
       </c>
-      <c r="K39">
+      <c r="P39">
         <v>50.0</v>
       </c>
-      <c r="N39">
+      <c r="S39">
         <v>0</v>
       </c>
     </row>
@@ -1614,18 +2160,33 @@
         <v>26.9</v>
       </c>
       <c r="I40">
+        <v>37.2</v>
+      </c>
+      <c r="J40">
+        <v>0.0</v>
+      </c>
+      <c r="K40">
+        <v>25.0</v>
+      </c>
+      <c r="L40">
+        <v>0.0</v>
+      </c>
+      <c r="M40">
         <v>0.7</v>
       </c>
-      <c r="J40">
+      <c r="N40">
+        <v>0.7</v>
+      </c>
+      <c r="O40">
         <v>37.2</v>
       </c>
-      <c r="L40">
-        <v>25.0</v>
-      </c>
-      <c r="M40">
+      <c r="Q40">
+        <v>25.0</v>
+      </c>
+      <c r="R40">
         <v>68.4</v>
       </c>
-      <c r="N40">
+      <c r="S40">
         <v>9</v>
       </c>
     </row>
@@ -1656,21 +2217,36 @@
         <v>64.5</v>
       </c>
       <c r="I41">
+        <v>7.0</v>
+      </c>
+      <c r="J41">
+        <v>0.0</v>
+      </c>
+      <c r="K41">
+        <v>17.5</v>
+      </c>
+      <c r="L41">
+        <v>2.3</v>
+      </c>
+      <c r="M41">
         <v>4.2</v>
       </c>
-      <c r="J41">
+      <c r="N41">
+        <v>4.2</v>
+      </c>
+      <c r="O41">
         <v>9.4</v>
       </c>
-      <c r="K41">
+      <c r="P41">
         <v>10.0</v>
       </c>
-      <c r="L41">
+      <c r="Q41">
         <v>20.0</v>
       </c>
-      <c r="M41">
+      <c r="R41">
         <v>80.2</v>
       </c>
-      <c r="N41">
+      <c r="S41">
         <v>5</v>
       </c>
     </row>
@@ -1701,21 +2277,36 @@
         <v>33.7</v>
       </c>
       <c r="I42">
+        <v>28.7</v>
+      </c>
+      <c r="J42">
+        <v>0.0</v>
+      </c>
+      <c r="K42">
+        <v>15.0</v>
+      </c>
+      <c r="L42">
+        <v>0.0</v>
+      </c>
+      <c r="M42">
         <v>34.2</v>
       </c>
-      <c r="J42">
+      <c r="N42">
+        <v>34.2</v>
+      </c>
+      <c r="O42">
         <v>28.7</v>
       </c>
-      <c r="K42">
+      <c r="P42">
         <v>10.0</v>
       </c>
-      <c r="L42">
+      <c r="Q42">
         <v>15.0</v>
       </c>
-      <c r="M42">
+      <c r="R42">
         <v>66.6</v>
       </c>
-      <c r="N42">
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
@@ -1746,18 +2337,30 @@
         <v>23.0</v>
       </c>
       <c r="I43">
+        <v>0.0</v>
+      </c>
+      <c r="J43">
+        <v>0.0</v>
+      </c>
+      <c r="L43">
+        <v>51.5</v>
+      </c>
+      <c r="M43">
         <v>53.7</v>
       </c>
-      <c r="J43">
+      <c r="N43">
+        <v>53.7</v>
+      </c>
+      <c r="O43">
         <v>51.5</v>
       </c>
-      <c r="K43">
-        <v>25.0</v>
-      </c>
-      <c r="L43">
+      <c r="P43">
+        <v>25.0</v>
+      </c>
+      <c r="Q43">
         <v>20.0</v>
       </c>
-      <c r="N43">
+      <c r="S43">
         <v>0</v>
       </c>
     </row>
@@ -1788,18 +2391,30 @@
         <v>15.9</v>
       </c>
       <c r="I44">
+        <v>0.0</v>
+      </c>
+      <c r="J44">
+        <v>0.0</v>
+      </c>
+      <c r="L44">
+        <v>8.6</v>
+      </c>
+      <c r="M44">
         <v>39.7</v>
       </c>
-      <c r="J44">
+      <c r="N44">
+        <v>39.7</v>
+      </c>
+      <c r="O44">
         <v>8.6</v>
       </c>
-      <c r="K44">
+      <c r="P44">
         <v>30.0</v>
       </c>
-      <c r="L44">
-        <v>25.0</v>
-      </c>
-      <c r="N44">
+      <c r="Q44">
+        <v>25.0</v>
+      </c>
+      <c r="S44">
         <v>0</v>
       </c>
     </row>
@@ -1829,13 +2444,19 @@
       <c r="H45">
         <v>94.7</v>
       </c>
-      <c r="I45">
+      <c r="J45">
+        <v>0.0</v>
+      </c>
+      <c r="M45">
         <v>23.1</v>
       </c>
-      <c r="K45">
+      <c r="N45">
+        <v>23.1</v>
+      </c>
+      <c r="P45">
         <v>40.0</v>
       </c>
-      <c r="N45">
+      <c r="S45">
         <v>0</v>
       </c>
     </row>
@@ -1865,13 +2486,22 @@
       <c r="H46">
         <v>0.0</v>
       </c>
-      <c r="J46">
+      <c r="I46">
+        <v>3.8</v>
+      </c>
+      <c r="K46">
+        <v>32.5</v>
+      </c>
+      <c r="L46">
+        <v>2.3</v>
+      </c>
+      <c r="O46">
         <v>6.1</v>
       </c>
-      <c r="L46">
+      <c r="Q46">
         <v>30.0</v>
       </c>
-      <c r="N46">
+      <c r="S46">
         <v>0</v>
       </c>
     </row>
@@ -1902,18 +2532,33 @@
         <v>12.8</v>
       </c>
       <c r="I47">
+        <v>65.6</v>
+      </c>
+      <c r="J47">
+        <v>0.0</v>
+      </c>
+      <c r="K47">
+        <v>35.0</v>
+      </c>
+      <c r="L47">
+        <v>0.0</v>
+      </c>
+      <c r="M47">
         <v>13.0</v>
       </c>
-      <c r="J47">
+      <c r="N47">
+        <v>13.0</v>
+      </c>
+      <c r="O47">
         <v>65.6</v>
       </c>
-      <c r="L47">
+      <c r="Q47">
         <v>35.0</v>
       </c>
-      <c r="M47">
+      <c r="R47">
         <v>54.8</v>
       </c>
-      <c r="N47">
+      <c r="S47">
         <v>4</v>
       </c>
     </row>
@@ -1944,21 +2589,36 @@
         <v>67.3</v>
       </c>
       <c r="I48">
+        <v>8.0</v>
+      </c>
+      <c r="J48">
+        <v>0.0</v>
+      </c>
+      <c r="K48">
+        <v>20.0</v>
+      </c>
+      <c r="L48">
+        <v>1.4</v>
+      </c>
+      <c r="M48">
         <v>5.3</v>
       </c>
-      <c r="J48">
+      <c r="N48">
+        <v>5.3</v>
+      </c>
+      <c r="O48">
         <v>9.4</v>
       </c>
-      <c r="K48">
+      <c r="P48">
         <v>10.0</v>
       </c>
-      <c r="L48">
+      <c r="Q48">
         <v>20.0</v>
       </c>
-      <c r="M48">
+      <c r="R48">
         <v>49.2</v>
       </c>
-      <c r="N48">
+      <c r="S48">
         <v>7</v>
       </c>
     </row>
@@ -1989,15 +2649,30 @@
         <v>11.3</v>
       </c>
       <c r="I49">
-        <v>0.0</v>
+        <v>59.2</v>
       </c>
       <c r="J49">
+        <v>0.0</v>
+      </c>
+      <c r="K49">
+        <v>40.0</v>
+      </c>
+      <c r="L49">
+        <v>0.3</v>
+      </c>
+      <c r="M49">
+        <v>0.0</v>
+      </c>
+      <c r="N49">
+        <v>0.0</v>
+      </c>
+      <c r="O49">
         <v>59.4</v>
       </c>
-      <c r="L49">
+      <c r="Q49">
         <v>40.0</v>
       </c>
-      <c r="N49">
+      <c r="S49">
         <v>1</v>
       </c>
     </row>
@@ -2028,18 +2703,33 @@
         <v>9.9</v>
       </c>
       <c r="I50">
+        <v>68.8</v>
+      </c>
+      <c r="J50">
+        <v>0.0</v>
+      </c>
+      <c r="K50">
+        <v>30.0</v>
+      </c>
+      <c r="L50">
+        <v>0.0</v>
+      </c>
+      <c r="M50">
         <v>2.5</v>
       </c>
-      <c r="J50">
+      <c r="N50">
+        <v>2.5</v>
+      </c>
+      <c r="O50">
         <v>68.8</v>
       </c>
-      <c r="L50">
+      <c r="Q50">
         <v>30.0</v>
       </c>
-      <c r="M50">
-        <v>25.0</v>
-      </c>
-      <c r="N50">
+      <c r="R50">
+        <v>25.0</v>
+      </c>
+      <c r="S50">
         <v>4</v>
       </c>
     </row>
@@ -2069,13 +2759,22 @@
       <c r="H51">
         <v>0.3</v>
       </c>
-      <c r="J51">
+      <c r="I51">
+        <v>19.4</v>
+      </c>
+      <c r="K51">
+        <v>20.0</v>
+      </c>
+      <c r="L51">
+        <v>1.3</v>
+      </c>
+      <c r="O51">
         <v>20.7</v>
       </c>
-      <c r="L51">
+      <c r="Q51">
         <v>20.0</v>
       </c>
-      <c r="N51">
+      <c r="S51">
         <v>0</v>
       </c>
     </row>
@@ -2105,13 +2804,22 @@
       <c r="H52">
         <v>0.0</v>
       </c>
-      <c r="J52">
+      <c r="I52">
+        <v>3.0</v>
+      </c>
+      <c r="K52">
+        <v>35.0</v>
+      </c>
+      <c r="L52">
+        <v>18.1</v>
+      </c>
+      <c r="O52">
         <v>21.1</v>
       </c>
-      <c r="L52">
+      <c r="Q52">
         <v>35.0</v>
       </c>
-      <c r="N52">
+      <c r="S52">
         <v>0</v>
       </c>
     </row>
@@ -2142,18 +2850,30 @@
         <v>25.8</v>
       </c>
       <c r="I53">
+        <v>0.0</v>
+      </c>
+      <c r="J53">
+        <v>0.0</v>
+      </c>
+      <c r="L53">
+        <v>33.3</v>
+      </c>
+      <c r="M53">
         <v>30.9</v>
       </c>
-      <c r="J53">
+      <c r="N53">
+        <v>30.9</v>
+      </c>
+      <c r="O53">
         <v>33.3</v>
       </c>
-      <c r="K53">
+      <c r="P53">
         <v>20.0</v>
       </c>
-      <c r="L53">
+      <c r="Q53">
         <v>20.0</v>
       </c>
-      <c r="N53">
+      <c r="S53">
         <v>0</v>
       </c>
     </row>
@@ -2184,21 +2904,36 @@
         <v>48.1</v>
       </c>
       <c r="I54">
+        <v>43.6</v>
+      </c>
+      <c r="J54">
+        <v>0.0</v>
+      </c>
+      <c r="K54">
+        <v>25.0</v>
+      </c>
+      <c r="L54">
+        <v>9.6</v>
+      </c>
+      <c r="M54">
         <v>19.0</v>
       </c>
-      <c r="J54">
+      <c r="N54">
+        <v>19.0</v>
+      </c>
+      <c r="O54">
         <v>53.2</v>
       </c>
-      <c r="K54">
+      <c r="P54">
         <v>20.0</v>
       </c>
-      <c r="L54">
-        <v>25.0</v>
-      </c>
-      <c r="M54">
+      <c r="Q54">
+        <v>25.0</v>
+      </c>
+      <c r="R54">
         <v>84.0</v>
       </c>
-      <c r="N54">
+      <c r="S54">
         <v>7</v>
       </c>
     </row>
@@ -2228,13 +2963,19 @@
       <c r="H55">
         <v>96.6</v>
       </c>
-      <c r="I55">
+      <c r="J55">
+        <v>0.0</v>
+      </c>
+      <c r="M55">
         <v>53.5</v>
       </c>
-      <c r="K55">
+      <c r="N55">
+        <v>53.5</v>
+      </c>
+      <c r="P55">
         <v>40.0</v>
       </c>
-      <c r="N55">
+      <c r="S55">
         <v>0</v>
       </c>
     </row>
@@ -2265,18 +3006,33 @@
         <v>20.9</v>
       </c>
       <c r="I56">
+        <v>38.8</v>
+      </c>
+      <c r="J56">
+        <v>0.0</v>
+      </c>
+      <c r="K56">
+        <v>25.0</v>
+      </c>
+      <c r="L56">
+        <v>0.0</v>
+      </c>
+      <c r="M56">
         <v>1.4</v>
       </c>
-      <c r="J56">
+      <c r="N56">
+        <v>1.4</v>
+      </c>
+      <c r="O56">
         <v>38.8</v>
       </c>
-      <c r="L56">
-        <v>25.0</v>
-      </c>
-      <c r="M56">
+      <c r="Q56">
+        <v>25.0</v>
+      </c>
+      <c r="R56">
         <v>53.6</v>
       </c>
-      <c r="N56">
+      <c r="S56">
         <v>5</v>
       </c>
     </row>
@@ -2307,18 +3063,33 @@
         <v>15.9</v>
       </c>
       <c r="I57">
+        <v>83.6</v>
+      </c>
+      <c r="J57">
+        <v>0.0</v>
+      </c>
+      <c r="K57">
+        <v>25.0</v>
+      </c>
+      <c r="L57">
+        <v>0.0</v>
+      </c>
+      <c r="M57">
         <v>5.7</v>
       </c>
-      <c r="J57">
+      <c r="N57">
+        <v>5.7</v>
+      </c>
+      <c r="O57">
         <v>83.6</v>
       </c>
-      <c r="L57">
-        <v>25.0</v>
-      </c>
-      <c r="M57">
+      <c r="Q57">
+        <v>25.0</v>
+      </c>
+      <c r="R57">
         <v>28.4</v>
       </c>
-      <c r="N57">
+      <c r="S57">
         <v>4</v>
       </c>
     </row>
@@ -2349,18 +3120,30 @@
         <v>63.2</v>
       </c>
       <c r="I58">
+        <v>7.4</v>
+      </c>
+      <c r="J58">
+        <v>0.0</v>
+      </c>
+      <c r="L58">
+        <v>0.8</v>
+      </c>
+      <c r="M58">
         <v>3.8</v>
       </c>
-      <c r="J58">
+      <c r="N58">
+        <v>3.8</v>
+      </c>
+      <c r="O58">
         <v>8.3</v>
       </c>
-      <c r="L58">
+      <c r="Q58">
         <v>10.0</v>
       </c>
-      <c r="M58">
+      <c r="R58">
         <v>82.1</v>
       </c>
-      <c r="N58">
+      <c r="S58">
         <v>6</v>
       </c>
     </row>
@@ -2391,15 +3174,27 @@
         <v>69.5</v>
       </c>
       <c r="I59">
+        <v>4.0</v>
+      </c>
+      <c r="J59">
+        <v>0.0</v>
+      </c>
+      <c r="L59">
+        <v>0.0</v>
+      </c>
+      <c r="M59">
         <v>2.6</v>
       </c>
-      <c r="J59">
+      <c r="N59">
+        <v>2.6</v>
+      </c>
+      <c r="O59">
         <v>4.0</v>
       </c>
-      <c r="M59">
+      <c r="R59">
         <v>65.8</v>
       </c>
-      <c r="N59">
+      <c r="S59">
         <v>4</v>
       </c>
     </row>
@@ -2429,13 +3224,19 @@
       <c r="H60">
         <v>95.7</v>
       </c>
-      <c r="I60">
+      <c r="J60">
+        <v>0.0</v>
+      </c>
+      <c r="M60">
         <v>7.3</v>
       </c>
-      <c r="K60">
+      <c r="N60">
+        <v>7.3</v>
+      </c>
+      <c r="P60">
         <v>50.0</v>
       </c>
-      <c r="N60">
+      <c r="S60">
         <v>0</v>
       </c>
     </row>
@@ -2466,18 +3267,30 @@
         <v>30.6</v>
       </c>
       <c r="I61">
+        <v>0.0</v>
+      </c>
+      <c r="J61">
+        <v>0.0</v>
+      </c>
+      <c r="L61">
+        <v>46.2</v>
+      </c>
+      <c r="M61">
         <v>29.3</v>
       </c>
-      <c r="J61">
+      <c r="N61">
+        <v>29.3</v>
+      </c>
+      <c r="O61">
         <v>46.2</v>
       </c>
-      <c r="K61">
+      <c r="P61">
         <v>20.0</v>
       </c>
-      <c r="L61">
+      <c r="Q61">
         <v>20.0</v>
       </c>
-      <c r="N61">
+      <c r="S61">
         <v>0</v>
       </c>
     </row>
@@ -2508,18 +3321,33 @@
         <v>35.2</v>
       </c>
       <c r="I62">
+        <v>53.4</v>
+      </c>
+      <c r="J62">
+        <v>0.0</v>
+      </c>
+      <c r="K62">
+        <v>35.0</v>
+      </c>
+      <c r="L62">
+        <v>0.0</v>
+      </c>
+      <c r="M62">
         <v>0.9</v>
       </c>
-      <c r="J62">
+      <c r="N62">
+        <v>0.9</v>
+      </c>
+      <c r="O62">
         <v>53.4</v>
       </c>
-      <c r="L62">
+      <c r="Q62">
         <v>35.0</v>
       </c>
-      <c r="M62">
+      <c r="R62">
         <v>60.5</v>
       </c>
-      <c r="N62">
+      <c r="S62">
         <v>2</v>
       </c>
     </row>
@@ -2550,18 +3378,33 @@
         <v>20.3</v>
       </c>
       <c r="I63">
-        <v>0.0</v>
+        <v>11.1</v>
       </c>
       <c r="J63">
+        <v>0.0</v>
+      </c>
+      <c r="K63">
+        <v>25.0</v>
+      </c>
+      <c r="L63">
+        <v>0.0</v>
+      </c>
+      <c r="M63">
+        <v>0.0</v>
+      </c>
+      <c r="N63">
+        <v>0.0</v>
+      </c>
+      <c r="O63">
         <v>11.1</v>
       </c>
-      <c r="L63">
-        <v>25.0</v>
-      </c>
-      <c r="M63">
+      <c r="Q63">
+        <v>25.0</v>
+      </c>
+      <c r="R63">
         <v>52.5</v>
       </c>
-      <c r="N63">
+      <c r="S63">
         <v>3</v>
       </c>
     </row>
@@ -2591,16 +3434,22 @@
       <c r="H64">
         <v>7.2</v>
       </c>
-      <c r="J64">
+      <c r="I64">
+        <v>0.0</v>
+      </c>
+      <c r="L64">
         <v>16.6</v>
       </c>
-      <c r="K64">
+      <c r="O64">
+        <v>16.6</v>
+      </c>
+      <c r="P64">
         <v>20.0</v>
       </c>
-      <c r="L64">
+      <c r="Q64">
         <v>20.0</v>
       </c>
-      <c r="N64">
+      <c r="S64">
         <v>0</v>
       </c>
     </row>
@@ -2631,15 +3480,27 @@
         <v>85.8</v>
       </c>
       <c r="I65">
+        <v>9.8</v>
+      </c>
+      <c r="J65">
+        <v>0.0</v>
+      </c>
+      <c r="L65">
+        <v>9.8</v>
+      </c>
+      <c r="M65">
         <v>34.4</v>
       </c>
-      <c r="J65">
+      <c r="N65">
+        <v>34.4</v>
+      </c>
+      <c r="O65">
         <v>19.5</v>
       </c>
-      <c r="K65">
+      <c r="P65">
         <v>30.0</v>
       </c>
-      <c r="N65">
+      <c r="S65">
         <v>0</v>
       </c>
     </row>
@@ -2669,13 +3530,19 @@
       <c r="H66">
         <v>0.0</v>
       </c>
-      <c r="J66">
+      <c r="I66">
+        <v>3.1</v>
+      </c>
+      <c r="L66">
+        <v>33.9</v>
+      </c>
+      <c r="O66">
         <v>37.1</v>
       </c>
-      <c r="L66">
+      <c r="Q66">
         <v>20.0</v>
       </c>
-      <c r="N66">
+      <c r="S66">
         <v>0</v>
       </c>
     </row>
@@ -2706,18 +3573,30 @@
         <v>64.0</v>
       </c>
       <c r="I67">
+        <v>0.0</v>
+      </c>
+      <c r="J67">
+        <v>0.0</v>
+      </c>
+      <c r="L67">
+        <v>34.0</v>
+      </c>
+      <c r="M67">
         <v>50.3</v>
       </c>
-      <c r="J67">
+      <c r="N67">
+        <v>50.3</v>
+      </c>
+      <c r="O67">
         <v>34.0</v>
       </c>
-      <c r="K67">
+      <c r="P67">
         <v>20.0</v>
       </c>
-      <c r="L67">
-        <v>25.0</v>
-      </c>
-      <c r="N67">
+      <c r="Q67">
+        <v>25.0</v>
+      </c>
+      <c r="S67">
         <v>0</v>
       </c>
     </row>
@@ -2747,13 +3626,19 @@
       <c r="H68">
         <v>0.0</v>
       </c>
-      <c r="J68">
+      <c r="I68">
+        <v>0.7</v>
+      </c>
+      <c r="L68">
+        <v>37.9</v>
+      </c>
+      <c r="O68">
         <v>38.6</v>
       </c>
-      <c r="L68">
+      <c r="Q68">
         <v>40.0</v>
       </c>
-      <c r="N68">
+      <c r="S68">
         <v>0</v>
       </c>
     </row>
@@ -2784,18 +3669,33 @@
         <v>16.5</v>
       </c>
       <c r="I69">
-        <v>0.0</v>
+        <v>41.8</v>
       </c>
       <c r="J69">
+        <v>0.0</v>
+      </c>
+      <c r="K69">
+        <v>20.0</v>
+      </c>
+      <c r="L69">
+        <v>0.0</v>
+      </c>
+      <c r="M69">
+        <v>0.0</v>
+      </c>
+      <c r="N69">
+        <v>0.0</v>
+      </c>
+      <c r="O69">
         <v>41.8</v>
       </c>
-      <c r="L69">
+      <c r="Q69">
         <v>20.0</v>
       </c>
-      <c r="M69">
+      <c r="R69">
         <v>88.3</v>
       </c>
-      <c r="N69">
+      <c r="S69">
         <v>2</v>
       </c>
     </row>
@@ -2826,18 +3726,33 @@
         <v>17.4</v>
       </c>
       <c r="I70">
+        <v>55.3</v>
+      </c>
+      <c r="J70">
+        <v>0.0</v>
+      </c>
+      <c r="K70">
+        <v>25.0</v>
+      </c>
+      <c r="L70">
+        <v>0.0</v>
+      </c>
+      <c r="M70">
         <v>4.3</v>
       </c>
-      <c r="J70">
+      <c r="N70">
+        <v>4.3</v>
+      </c>
+      <c r="O70">
         <v>55.3</v>
       </c>
-      <c r="L70">
-        <v>25.0</v>
-      </c>
-      <c r="M70">
+      <c r="Q70">
+        <v>25.0</v>
+      </c>
+      <c r="R70">
         <v>44.5</v>
       </c>
-      <c r="N70">
+      <c r="S70">
         <v>4</v>
       </c>
     </row>
@@ -2867,13 +3782,22 @@
       <c r="H71">
         <v>0.0</v>
       </c>
-      <c r="J71">
+      <c r="I71">
+        <v>6.7</v>
+      </c>
+      <c r="K71">
+        <v>35.0</v>
+      </c>
+      <c r="L71">
+        <v>11.8</v>
+      </c>
+      <c r="O71">
         <v>18.5</v>
       </c>
-      <c r="L71">
+      <c r="Q71">
         <v>30.0</v>
       </c>
-      <c r="N71">
+      <c r="S71">
         <v>0</v>
       </c>
     </row>
@@ -2903,13 +3827,22 @@
       <c r="H72">
         <v>0.0</v>
       </c>
-      <c r="J72">
+      <c r="I72">
+        <v>6.8</v>
+      </c>
+      <c r="K72">
+        <v>30.0</v>
+      </c>
+      <c r="L72">
+        <v>13.6</v>
+      </c>
+      <c r="O72">
         <v>20.4</v>
       </c>
-      <c r="L72">
-        <v>25.0</v>
-      </c>
-      <c r="N72">
+      <c r="Q72">
+        <v>25.0</v>
+      </c>
+      <c r="S72">
         <v>0</v>
       </c>
     </row>
@@ -2940,18 +3873,33 @@
         <v>28.6</v>
       </c>
       <c r="I73">
-        <v>0.0</v>
+        <v>73.7</v>
       </c>
       <c r="J73">
+        <v>0.0</v>
+      </c>
+      <c r="K73">
+        <v>40.0</v>
+      </c>
+      <c r="L73">
+        <v>2.6</v>
+      </c>
+      <c r="M73">
+        <v>0.0</v>
+      </c>
+      <c r="N73">
+        <v>0.0</v>
+      </c>
+      <c r="O73">
         <v>76.3</v>
       </c>
-      <c r="L73">
+      <c r="Q73">
         <v>40.0</v>
       </c>
-      <c r="M73">
+      <c r="R73">
         <v>53.9</v>
       </c>
-      <c r="N73">
+      <c r="S73">
         <v>4</v>
       </c>
     </row>
@@ -2982,18 +3930,33 @@
         <v>19.8</v>
       </c>
       <c r="I74">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="J74">
+        <v>0.0</v>
+      </c>
+      <c r="K74">
+        <v>30.0</v>
+      </c>
+      <c r="L74">
+        <v>0.0</v>
+      </c>
+      <c r="M74">
+        <v>0.0</v>
+      </c>
+      <c r="N74">
+        <v>0.0</v>
+      </c>
+      <c r="O74">
         <v>60.0</v>
       </c>
-      <c r="L74">
+      <c r="Q74">
         <v>30.0</v>
       </c>
-      <c r="M74">
+      <c r="R74">
         <v>55.9</v>
       </c>
-      <c r="N74">
+      <c r="S74">
         <v>4</v>
       </c>
     </row>
@@ -3023,13 +3986,22 @@
       <c r="H75">
         <v>0.0</v>
       </c>
-      <c r="J75">
+      <c r="I75">
+        <v>8.1</v>
+      </c>
+      <c r="K75">
+        <v>30.0</v>
+      </c>
+      <c r="L75">
+        <v>11.0</v>
+      </c>
+      <c r="O75">
         <v>19.0</v>
       </c>
-      <c r="L75">
+      <c r="Q75">
         <v>27.5</v>
       </c>
-      <c r="N75">
+      <c r="S75">
         <v>0</v>
       </c>
     </row>
@@ -3060,18 +4032,33 @@
         <v>20.9</v>
       </c>
       <c r="I76">
-        <v>0.0</v>
+        <v>28.3</v>
       </c>
       <c r="J76">
+        <v>0.0</v>
+      </c>
+      <c r="K76">
+        <v>25.0</v>
+      </c>
+      <c r="L76">
+        <v>0.0</v>
+      </c>
+      <c r="M76">
+        <v>0.0</v>
+      </c>
+      <c r="N76">
+        <v>0.0</v>
+      </c>
+      <c r="O76">
         <v>28.3</v>
       </c>
-      <c r="L76">
-        <v>25.0</v>
-      </c>
-      <c r="M76">
+      <c r="Q76">
+        <v>25.0</v>
+      </c>
+      <c r="R76">
         <v>53.6</v>
       </c>
-      <c r="N76">
+      <c r="S76">
         <v>3</v>
       </c>
     </row>
@@ -3102,18 +4089,33 @@
         <v>17.5</v>
       </c>
       <c r="I77">
+        <v>63.6</v>
+      </c>
+      <c r="J77">
+        <v>0.0</v>
+      </c>
+      <c r="K77">
+        <v>35.0</v>
+      </c>
+      <c r="L77">
+        <v>3.6</v>
+      </c>
+      <c r="M77">
         <v>25.7</v>
       </c>
-      <c r="J77">
+      <c r="N77">
+        <v>25.7</v>
+      </c>
+      <c r="O77">
         <v>67.3</v>
       </c>
-      <c r="L77">
+      <c r="Q77">
         <v>35.0</v>
       </c>
-      <c r="M77">
+      <c r="R77">
         <v>61.9</v>
       </c>
-      <c r="N77">
+      <c r="S77">
         <v>2</v>
       </c>
     </row>
@@ -3144,18 +4146,33 @@
         <v>26.0</v>
       </c>
       <c r="I78">
-        <v>0.0</v>
+        <v>23.6</v>
       </c>
       <c r="J78">
+        <v>0.0</v>
+      </c>
+      <c r="K78">
+        <v>25.0</v>
+      </c>
+      <c r="L78">
+        <v>0.0</v>
+      </c>
+      <c r="M78">
+        <v>0.0</v>
+      </c>
+      <c r="N78">
+        <v>0.0</v>
+      </c>
+      <c r="O78">
         <v>23.6</v>
       </c>
-      <c r="L78">
-        <v>25.0</v>
-      </c>
-      <c r="M78">
+      <c r="Q78">
+        <v>25.0</v>
+      </c>
+      <c r="R78">
         <v>64.6</v>
       </c>
-      <c r="N78">
+      <c r="S78">
         <v>2</v>
       </c>
     </row>
@@ -3185,13 +4202,22 @@
       <c r="H79">
         <v>0.0</v>
       </c>
-      <c r="J79">
+      <c r="I79">
+        <v>5.7</v>
+      </c>
+      <c r="K79">
+        <v>20.0</v>
+      </c>
+      <c r="L79">
+        <v>14.9</v>
+      </c>
+      <c r="O79">
         <v>20.6</v>
       </c>
-      <c r="L79">
-        <v>25.0</v>
-      </c>
-      <c r="N79">
+      <c r="Q79">
+        <v>25.0</v>
+      </c>
+      <c r="S79">
         <v>0</v>
       </c>
     </row>
@@ -3221,13 +4247,22 @@
       <c r="H80">
         <v>0.0</v>
       </c>
-      <c r="J80">
+      <c r="I80">
         <v>75.4</v>
       </c>
+      <c r="K80">
+        <v>25.0</v>
+      </c>
       <c r="L80">
-        <v>25.0</v>
-      </c>
-      <c r="N80">
+        <v>0.0</v>
+      </c>
+      <c r="O80">
+        <v>75.4</v>
+      </c>
+      <c r="Q80">
+        <v>25.0</v>
+      </c>
+      <c r="S80">
         <v>0</v>
       </c>
     </row>
@@ -3258,18 +4293,33 @@
         <v>24.0</v>
       </c>
       <c r="I81">
-        <v>0.0</v>
+        <v>89.2</v>
       </c>
       <c r="J81">
+        <v>0.0</v>
+      </c>
+      <c r="K81">
+        <v>35.0</v>
+      </c>
+      <c r="L81">
+        <v>0.7</v>
+      </c>
+      <c r="M81">
+        <v>0.0</v>
+      </c>
+      <c r="N81">
+        <v>0.0</v>
+      </c>
+      <c r="O81">
         <v>89.9</v>
       </c>
-      <c r="L81">
+      <c r="Q81">
         <v>35.0</v>
       </c>
-      <c r="M81">
+      <c r="R81">
         <v>42.0</v>
       </c>
-      <c r="N81">
+      <c r="S81">
         <v>2</v>
       </c>
     </row>
@@ -3299,13 +4349,22 @@
       <c r="H82">
         <v>0.0</v>
       </c>
-      <c r="J82">
+      <c r="I82">
+        <v>7.2</v>
+      </c>
+      <c r="K82">
+        <v>30.0</v>
+      </c>
+      <c r="L82">
+        <v>4.4</v>
+      </c>
+      <c r="O82">
         <v>11.6</v>
       </c>
-      <c r="L82">
+      <c r="Q82">
         <v>30.0</v>
       </c>
-      <c r="N82">
+      <c r="S82">
         <v>0</v>
       </c>
     </row>
@@ -3336,15 +4395,27 @@
         <v>58.0</v>
       </c>
       <c r="I83">
+        <v>0.0</v>
+      </c>
+      <c r="J83">
+        <v>0.0</v>
+      </c>
+      <c r="L83">
+        <v>5.3</v>
+      </c>
+      <c r="M83">
         <v>26.7</v>
       </c>
-      <c r="J83">
+      <c r="N83">
+        <v>26.7</v>
+      </c>
+      <c r="O83">
         <v>5.3</v>
       </c>
-      <c r="K83">
+      <c r="P83">
         <v>20.0</v>
       </c>
-      <c r="N83">
+      <c r="S83">
         <v>0</v>
       </c>
     </row>
@@ -3374,13 +4445,19 @@
       <c r="H84">
         <v>0.0</v>
       </c>
-      <c r="J84">
+      <c r="I84">
+        <v>0.0</v>
+      </c>
+      <c r="L84">
         <v>11.7</v>
       </c>
-      <c r="L84">
+      <c r="O84">
+        <v>11.7</v>
+      </c>
+      <c r="Q84">
         <v>20.0</v>
       </c>
-      <c r="N84">
+      <c r="S84">
         <v>0</v>
       </c>
     </row>
@@ -3411,18 +4488,33 @@
         <v>19.4</v>
       </c>
       <c r="I85">
-        <v>0.0</v>
+        <v>30.8</v>
       </c>
       <c r="J85">
+        <v>0.0</v>
+      </c>
+      <c r="K85">
+        <v>20.0</v>
+      </c>
+      <c r="L85">
+        <v>0.0</v>
+      </c>
+      <c r="M85">
+        <v>0.0</v>
+      </c>
+      <c r="N85">
+        <v>0.0</v>
+      </c>
+      <c r="O85">
         <v>30.8</v>
       </c>
-      <c r="L85">
+      <c r="Q85">
         <v>20.0</v>
       </c>
-      <c r="M85">
+      <c r="R85">
         <v>78.6</v>
       </c>
-      <c r="N85">
+      <c r="S85">
         <v>2</v>
       </c>
     </row>
@@ -3452,13 +4544,22 @@
       <c r="H86">
         <v>12.2</v>
       </c>
-      <c r="J86">
+      <c r="I86">
         <v>44.4</v>
       </c>
+      <c r="K86">
+        <v>15.0</v>
+      </c>
       <c r="L86">
+        <v>0.0</v>
+      </c>
+      <c r="O86">
+        <v>44.4</v>
+      </c>
+      <c r="Q86">
         <v>15.0</v>
       </c>
-      <c r="N86">
+      <c r="S86">
         <v>1</v>
       </c>
     </row>
@@ -3488,16 +4589,25 @@
       <c r="H87">
         <v>16.0</v>
       </c>
-      <c r="J87">
+      <c r="I87">
         <v>83.2</v>
       </c>
       <c r="K87">
+        <v>40.0</v>
+      </c>
+      <c r="L87">
+        <v>0.0</v>
+      </c>
+      <c r="O87">
+        <v>83.2</v>
+      </c>
+      <c r="P87">
         <v>20.0</v>
       </c>
-      <c r="L87">
+      <c r="Q87">
         <v>40.0</v>
       </c>
-      <c r="N87">
+      <c r="S87">
         <v>1</v>
       </c>
     </row>
@@ -3527,13 +4637,22 @@
       <c r="H88">
         <v>0.0</v>
       </c>
-      <c r="J88">
+      <c r="I88">
         <v>17.6</v>
       </c>
+      <c r="K88">
+        <v>10.0</v>
+      </c>
       <c r="L88">
+        <v>0.0</v>
+      </c>
+      <c r="O88">
+        <v>17.6</v>
+      </c>
+      <c r="Q88">
         <v>10.0</v>
       </c>
-      <c r="N88">
+      <c r="S88">
         <v>0</v>
       </c>
     </row>
@@ -3564,15 +4683,27 @@
         <v>51.0</v>
       </c>
       <c r="I89">
+        <v>0.0</v>
+      </c>
+      <c r="J89">
+        <v>0.0</v>
+      </c>
+      <c r="L89">
+        <v>11.3</v>
+      </c>
+      <c r="M89">
         <v>20.3</v>
       </c>
-      <c r="J89">
+      <c r="N89">
+        <v>20.3</v>
+      </c>
+      <c r="O89">
         <v>11.3</v>
       </c>
-      <c r="K89">
+      <c r="P89">
         <v>15.0</v>
       </c>
-      <c r="N89">
+      <c r="S89">
         <v>0</v>
       </c>
     </row>
@@ -3602,13 +4733,19 @@
       <c r="H90">
         <v>0.0</v>
       </c>
-      <c r="J90">
+      <c r="I90">
+        <v>0.0</v>
+      </c>
+      <c r="L90">
         <v>34.5</v>
       </c>
-      <c r="L90">
+      <c r="O90">
+        <v>34.5</v>
+      </c>
+      <c r="Q90">
         <v>15.0</v>
       </c>
-      <c r="N90">
+      <c r="S90">
         <v>0</v>
       </c>
     </row>
@@ -3638,16 +4775,25 @@
       <c r="H91">
         <v>20.9</v>
       </c>
-      <c r="J91">
+      <c r="I91">
         <v>80.9</v>
       </c>
+      <c r="K91">
+        <v>50.0</v>
+      </c>
       <c r="L91">
+        <v>0.0</v>
+      </c>
+      <c r="O91">
+        <v>80.9</v>
+      </c>
+      <c r="Q91">
         <v>50.0</v>
       </c>
-      <c r="M91">
+      <c r="R91">
         <v>55.4</v>
       </c>
-      <c r="N91">
+      <c r="S91">
         <v>2</v>
       </c>
     </row>
@@ -3677,13 +4823,22 @@
       <c r="H92">
         <v>20.5</v>
       </c>
-      <c r="J92">
+      <c r="I92">
         <v>31.4</v>
       </c>
+      <c r="K92">
+        <v>20.0</v>
+      </c>
       <c r="L92">
+        <v>0.0</v>
+      </c>
+      <c r="O92">
+        <v>31.4</v>
+      </c>
+      <c r="Q92">
         <v>20.0</v>
       </c>
-      <c r="N92">
+      <c r="S92">
         <v>0</v>
       </c>
     </row>
@@ -3713,13 +4868,22 @@
       <c r="H93">
         <v>0.0</v>
       </c>
-      <c r="J93">
+      <c r="I93">
+        <v>9.2</v>
+      </c>
+      <c r="K93">
+        <v>22.5</v>
+      </c>
+      <c r="L93">
+        <v>8.4</v>
+      </c>
+      <c r="O93">
         <v>17.6</v>
       </c>
-      <c r="L93">
+      <c r="Q93">
         <v>20.0</v>
       </c>
-      <c r="N93">
+      <c r="S93">
         <v>0</v>
       </c>
     </row>
@@ -3749,16 +4913,25 @@
       <c r="H94">
         <v>18.5</v>
       </c>
-      <c r="J94">
+      <c r="I94">
         <v>50.9</v>
       </c>
+      <c r="K94">
+        <v>30.0</v>
+      </c>
       <c r="L94">
+        <v>0.0</v>
+      </c>
+      <c r="O94">
+        <v>50.9</v>
+      </c>
+      <c r="Q94">
         <v>30.0</v>
       </c>
-      <c r="M94">
+      <c r="R94">
         <v>52.8</v>
       </c>
-      <c r="N94">
+      <c r="S94">
         <v>2</v>
       </c>
     </row>
@@ -3788,13 +4961,22 @@
       <c r="H95">
         <v>9.5</v>
       </c>
-      <c r="J95">
+      <c r="I95">
+        <v>14.0</v>
+      </c>
+      <c r="K95">
+        <v>15.0</v>
+      </c>
+      <c r="L95">
+        <v>1.8</v>
+      </c>
+      <c r="O95">
         <v>15.8</v>
       </c>
-      <c r="L95">
+      <c r="Q95">
         <v>15.0</v>
       </c>
-      <c r="N95">
+      <c r="S95">
         <v>0</v>
       </c>
     </row>
@@ -3824,13 +5006,22 @@
       <c r="H96">
         <v>0.0</v>
       </c>
-      <c r="J96">
+      <c r="I96">
+        <v>8.9</v>
+      </c>
+      <c r="K96">
+        <v>35.0</v>
+      </c>
+      <c r="L96">
+        <v>18.5</v>
+      </c>
+      <c r="O96">
         <v>27.4</v>
       </c>
-      <c r="L96">
+      <c r="Q96">
         <v>30.0</v>
       </c>
-      <c r="N96">
+      <c r="S96">
         <v>0</v>
       </c>
     </row>
@@ -3861,18 +5052,33 @@
         <v>40.7</v>
       </c>
       <c r="I97">
-        <v>0.0</v>
+        <v>21.9</v>
       </c>
       <c r="J97">
+        <v>0.0</v>
+      </c>
+      <c r="K97">
+        <v>25.0</v>
+      </c>
+      <c r="L97">
+        <v>0.0</v>
+      </c>
+      <c r="M97">
+        <v>0.0</v>
+      </c>
+      <c r="N97">
+        <v>0.0</v>
+      </c>
+      <c r="O97">
         <v>21.9</v>
       </c>
-      <c r="L97">
-        <v>25.0</v>
-      </c>
-      <c r="M97">
+      <c r="Q97">
+        <v>25.0</v>
+      </c>
+      <c r="R97">
         <v>34.8</v>
       </c>
-      <c r="N97">
+      <c r="S97">
         <v>3</v>
       </c>
     </row>
@@ -3902,10 +5108,16 @@
       <c r="H98">
         <v>0.0</v>
       </c>
-      <c r="J98">
+      <c r="I98">
+        <v>6.1</v>
+      </c>
+      <c r="L98">
+        <v>1.8</v>
+      </c>
+      <c r="O98">
         <v>7.9</v>
       </c>
-      <c r="N98">
+      <c r="S98">
         <v>0</v>
       </c>
     </row>
@@ -3935,13 +5147,19 @@
       <c r="H99">
         <v>0.0</v>
       </c>
-      <c r="J99">
+      <c r="I99">
+        <v>0.0</v>
+      </c>
+      <c r="L99">
         <v>68.8</v>
       </c>
-      <c r="L99">
+      <c r="O99">
+        <v>68.8</v>
+      </c>
+      <c r="Q99">
         <v>20.0</v>
       </c>
-      <c r="N99">
+      <c r="S99">
         <v>0</v>
       </c>
     </row>
@@ -3971,10 +5189,16 @@
       <c r="H100">
         <v>0.0</v>
       </c>
-      <c r="J100">
+      <c r="I100">
+        <v>0.0</v>
+      </c>
+      <c r="L100">
         <v>6.4</v>
       </c>
-      <c r="N100">
+      <c r="O100">
+        <v>6.4</v>
+      </c>
+      <c r="S100">
         <v>0</v>
       </c>
     </row>
@@ -4005,18 +5229,33 @@
         <v>31.4</v>
       </c>
       <c r="I101">
-        <v>0.0</v>
+        <v>43.1</v>
       </c>
       <c r="J101">
+        <v>0.0</v>
+      </c>
+      <c r="K101">
+        <v>25.0</v>
+      </c>
+      <c r="L101">
+        <v>1.4</v>
+      </c>
+      <c r="M101">
+        <v>0.0</v>
+      </c>
+      <c r="N101">
+        <v>0.0</v>
+      </c>
+      <c r="O101">
         <v>44.4</v>
       </c>
-      <c r="L101">
-        <v>25.0</v>
-      </c>
-      <c r="M101">
+      <c r="Q101">
+        <v>25.0</v>
+      </c>
+      <c r="R101">
         <v>47.1</v>
       </c>
-      <c r="N101">
+      <c r="S101">
         <v>3</v>
       </c>
     </row>
@@ -4046,10 +5285,16 @@
       <c r="H102">
         <v>0.0</v>
       </c>
-      <c r="J102">
+      <c r="I102">
+        <v>0.0</v>
+      </c>
+      <c r="L102">
         <v>1.9</v>
       </c>
-      <c r="N102">
+      <c r="O102">
+        <v>1.9</v>
+      </c>
+      <c r="S102">
         <v>0</v>
       </c>
     </row>
@@ -4079,13 +5324,19 @@
       <c r="H103">
         <v>0.0</v>
       </c>
-      <c r="J103">
+      <c r="I103">
+        <v>0.0</v>
+      </c>
+      <c r="L103">
         <v>31.5</v>
       </c>
-      <c r="L103">
-        <v>25.0</v>
-      </c>
-      <c r="N103">
+      <c r="O103">
+        <v>31.5</v>
+      </c>
+      <c r="Q103">
+        <v>25.0</v>
+      </c>
+      <c r="S103">
         <v>0</v>
       </c>
     </row>
@@ -4115,13 +5366,22 @@
       <c r="H104">
         <v>19.1</v>
       </c>
-      <c r="J104">
+      <c r="I104">
         <v>30.6</v>
       </c>
+      <c r="K104">
+        <v>25.0</v>
+      </c>
       <c r="L104">
-        <v>25.0</v>
-      </c>
-      <c r="N104">
+        <v>0.0</v>
+      </c>
+      <c r="O104">
+        <v>30.6</v>
+      </c>
+      <c r="Q104">
+        <v>25.0</v>
+      </c>
+      <c r="S104">
         <v>1</v>
       </c>
     </row>
@@ -4151,13 +5411,22 @@
       <c r="H105">
         <v>0.0</v>
       </c>
-      <c r="J105">
+      <c r="I105">
         <v>96.6</v>
       </c>
+      <c r="K105">
+        <v>30.0</v>
+      </c>
       <c r="L105">
+        <v>0.0</v>
+      </c>
+      <c r="O105">
+        <v>96.6</v>
+      </c>
+      <c r="Q105">
         <v>30.0</v>
       </c>
-      <c r="N105">
+      <c r="S105">
         <v>0</v>
       </c>
     </row>
@@ -4187,13 +5456,22 @@
       <c r="H106">
         <v>18.4</v>
       </c>
-      <c r="J106">
+      <c r="I106">
         <v>46.5</v>
       </c>
+      <c r="K106">
+        <v>10.0</v>
+      </c>
       <c r="L106">
+        <v>0.0</v>
+      </c>
+      <c r="O106">
+        <v>46.5</v>
+      </c>
+      <c r="Q106">
         <v>10.0</v>
       </c>
-      <c r="N106">
+      <c r="S106">
         <v>1</v>
       </c>
     </row>
@@ -4223,10 +5501,16 @@
       <c r="H107">
         <v>0.0</v>
       </c>
-      <c r="J107">
-        <v>0.0</v>
-      </c>
-      <c r="N107">
+      <c r="I107">
+        <v>0.0</v>
+      </c>
+      <c r="L107">
+        <v>0.0</v>
+      </c>
+      <c r="O107">
+        <v>0.0</v>
+      </c>
+      <c r="S107">
         <v>0</v>
       </c>
     </row>
@@ -4256,13 +5540,19 @@
       <c r="H108">
         <v>67.5</v>
       </c>
-      <c r="I108">
+      <c r="J108">
         <v>0.0</v>
       </c>
       <c r="M108">
+        <v>0.0</v>
+      </c>
+      <c r="N108">
+        <v>0.0</v>
+      </c>
+      <c r="R108">
         <v>40.9</v>
       </c>
-      <c r="N108">
+      <c r="S108">
         <v>3</v>
       </c>
     </row>
@@ -4292,16 +5582,25 @@
       <c r="H109">
         <v>28.0</v>
       </c>
-      <c r="J109">
+      <c r="I109">
         <v>86.4</v>
       </c>
+      <c r="K109">
+        <v>25.0</v>
+      </c>
       <c r="L109">
-        <v>25.0</v>
-      </c>
-      <c r="M109">
+        <v>0.0</v>
+      </c>
+      <c r="O109">
+        <v>86.4</v>
+      </c>
+      <c r="Q109">
+        <v>25.0</v>
+      </c>
+      <c r="R109">
         <v>46.2</v>
       </c>
-      <c r="N109">
+      <c r="S109">
         <v>2</v>
       </c>
     </row>
@@ -4331,13 +5630,22 @@
       <c r="H110">
         <v>23.2</v>
       </c>
-      <c r="J110">
+      <c r="I110">
         <v>22.2</v>
       </c>
+      <c r="K110">
+        <v>35.0</v>
+      </c>
       <c r="L110">
+        <v>0.0</v>
+      </c>
+      <c r="O110">
+        <v>22.2</v>
+      </c>
+      <c r="Q110">
         <v>35.0</v>
       </c>
-      <c r="N110">
+      <c r="S110">
         <v>1</v>
       </c>
     </row>
@@ -4367,13 +5675,22 @@
       <c r="H111">
         <v>0.0</v>
       </c>
-      <c r="J111">
+      <c r="I111">
         <v>37.0</v>
       </c>
+      <c r="K111">
+        <v>25.0</v>
+      </c>
       <c r="L111">
-        <v>25.0</v>
-      </c>
-      <c r="N111">
+        <v>0.0</v>
+      </c>
+      <c r="O111">
+        <v>37.0</v>
+      </c>
+      <c r="Q111">
+        <v>25.0</v>
+      </c>
+      <c r="S111">
         <v>0</v>
       </c>
     </row>
@@ -4403,10 +5720,16 @@
       <c r="H112">
         <v>0.0</v>
       </c>
-      <c r="J112">
+      <c r="I112">
+        <v>0.0</v>
+      </c>
+      <c r="L112">
         <v>1.4</v>
       </c>
-      <c r="N112">
+      <c r="O112">
+        <v>1.4</v>
+      </c>
+      <c r="S112">
         <v>0</v>
       </c>
     </row>
@@ -4436,16 +5759,25 @@
       <c r="H113">
         <v>32.8</v>
       </c>
-      <c r="J113">
+      <c r="I113">
         <v>51.1</v>
       </c>
+      <c r="K113">
+        <v>20.0</v>
+      </c>
       <c r="L113">
+        <v>0.0</v>
+      </c>
+      <c r="O113">
+        <v>51.1</v>
+      </c>
+      <c r="Q113">
         <v>20.0</v>
       </c>
-      <c r="M113">
+      <c r="R113">
         <v>57.6</v>
       </c>
-      <c r="N113">
+      <c r="S113">
         <v>2</v>
       </c>
     </row>
@@ -4475,13 +5807,22 @@
       <c r="H114">
         <v>20.0</v>
       </c>
-      <c r="J114">
+      <c r="I114">
         <v>26.9</v>
       </c>
+      <c r="K114">
+        <v>15.0</v>
+      </c>
       <c r="L114">
+        <v>0.0</v>
+      </c>
+      <c r="O114">
+        <v>26.9</v>
+      </c>
+      <c r="Q114">
         <v>15.0</v>
       </c>
-      <c r="N114">
+      <c r="S114">
         <v>0</v>
       </c>
     </row>
@@ -4511,13 +5852,22 @@
       <c r="H115">
         <v>37.1</v>
       </c>
-      <c r="J115">
+      <c r="I115">
         <v>35.9</v>
       </c>
+      <c r="K115">
+        <v>25.0</v>
+      </c>
       <c r="L115">
-        <v>25.0</v>
-      </c>
-      <c r="N115">
+        <v>0.0</v>
+      </c>
+      <c r="O115">
+        <v>35.9</v>
+      </c>
+      <c r="Q115">
+        <v>25.0</v>
+      </c>
+      <c r="S115">
         <v>1</v>
       </c>
     </row>
@@ -4547,13 +5897,19 @@
       <c r="H116">
         <v>0.0</v>
       </c>
-      <c r="J116">
+      <c r="I116">
+        <v>0.0</v>
+      </c>
+      <c r="L116">
         <v>28.3</v>
       </c>
-      <c r="L116">
+      <c r="O116">
+        <v>28.3</v>
+      </c>
+      <c r="Q116">
         <v>30.0</v>
       </c>
-      <c r="N116">
+      <c r="S116">
         <v>0</v>
       </c>
     </row>
@@ -4588,13 +5944,22 @@
       <c r="H117">
         <v>0.1</v>
       </c>
-      <c r="J117">
+      <c r="I117">
+        <v>24.8</v>
+      </c>
+      <c r="K117">
+        <v>30.0</v>
+      </c>
+      <c r="L117">
+        <v>2.2</v>
+      </c>
+      <c r="O117">
         <v>27.0</v>
       </c>
-      <c r="L117">
+      <c r="Q117">
         <v>30.0</v>
       </c>
-      <c r="N117">
+      <c r="S117">
         <v>0</v>
       </c>
     </row>
@@ -4629,13 +5994,22 @@
       <c r="H118">
         <v>0.2</v>
       </c>
-      <c r="J118">
+      <c r="I118">
+        <v>24.6</v>
+      </c>
+      <c r="K118">
+        <v>27.5</v>
+      </c>
+      <c r="L118">
+        <v>2.3</v>
+      </c>
+      <c r="O118">
         <v>27.0</v>
       </c>
-      <c r="L118">
-        <v>25.0</v>
-      </c>
-      <c r="N118">
+      <c r="Q118">
+        <v>25.0</v>
+      </c>
+      <c r="S118">
         <v>0</v>
       </c>
     </row>
@@ -4670,13 +6044,22 @@
       <c r="H119">
         <v>0.0</v>
       </c>
-      <c r="J119">
+      <c r="I119">
+        <v>7.2</v>
+      </c>
+      <c r="K119">
+        <v>20.0</v>
+      </c>
+      <c r="L119">
+        <v>0.2</v>
+      </c>
+      <c r="O119">
         <v>7.4</v>
       </c>
-      <c r="L119">
+      <c r="Q119">
         <v>20.0</v>
       </c>
-      <c r="N119">
+      <c r="S119">
         <v>0</v>
       </c>
     </row>
@@ -4711,10 +6094,16 @@
       <c r="H120">
         <v>0.0</v>
       </c>
-      <c r="J120">
+      <c r="I120">
         <v>2.0</v>
       </c>
-      <c r="N120">
+      <c r="L120">
+        <v>0.0</v>
+      </c>
+      <c r="O120">
+        <v>2.0</v>
+      </c>
+      <c r="S120">
         <v>0</v>
       </c>
     </row>
@@ -4749,13 +6138,22 @@
       <c r="H121">
         <v>0.3</v>
       </c>
-      <c r="J121">
+      <c r="I121">
+        <v>21.7</v>
+      </c>
+      <c r="K121">
+        <v>20.0</v>
+      </c>
+      <c r="L121">
+        <v>1.5</v>
+      </c>
+      <c r="O121">
         <v>23.1</v>
       </c>
-      <c r="L121">
+      <c r="Q121">
         <v>20.0</v>
       </c>
-      <c r="N121">
+      <c r="S121">
         <v>0</v>
       </c>
     </row>
@@ -4790,13 +6188,22 @@
       <c r="H122">
         <v>0.6</v>
       </c>
-      <c r="J122">
+      <c r="I122">
+        <v>28.3</v>
+      </c>
+      <c r="K122">
+        <v>25.0</v>
+      </c>
+      <c r="L122">
+        <v>3.5</v>
+      </c>
+      <c r="O122">
         <v>31.7</v>
       </c>
-      <c r="L122">
-        <v>25.0</v>
-      </c>
-      <c r="N122">
+      <c r="Q122">
+        <v>25.0</v>
+      </c>
+      <c r="S122">
         <v>0</v>
       </c>
     </row>
@@ -4832,18 +6239,30 @@
         <v>40.6</v>
       </c>
       <c r="I123">
+        <v>3.2</v>
+      </c>
+      <c r="J123">
+        <v>0.0</v>
+      </c>
+      <c r="L123">
+        <v>5.3</v>
+      </c>
+      <c r="M123">
         <v>46.1</v>
       </c>
-      <c r="J123">
+      <c r="N123">
+        <v>46.1</v>
+      </c>
+      <c r="O123">
         <v>8.6</v>
       </c>
-      <c r="K123">
+      <c r="P123">
         <v>40.0</v>
       </c>
-      <c r="L123">
-        <v>25.0</v>
-      </c>
-      <c r="N123">
+      <c r="Q123">
+        <v>25.0</v>
+      </c>
+      <c r="S123">
         <v>0</v>
       </c>
     </row>
@@ -4879,21 +6298,36 @@
         <v>19.9</v>
       </c>
       <c r="I124">
+        <v>60.2</v>
+      </c>
+      <c r="J124">
+        <v>0.0</v>
+      </c>
+      <c r="K124">
+        <v>25.0</v>
+      </c>
+      <c r="L124">
+        <v>0.0</v>
+      </c>
+      <c r="M124">
         <v>24.6</v>
       </c>
-      <c r="J124">
+      <c r="N124">
+        <v>24.6</v>
+      </c>
+      <c r="O124">
         <v>60.2</v>
       </c>
-      <c r="K124">
+      <c r="P124">
         <v>20.0</v>
       </c>
-      <c r="L124">
-        <v>25.0</v>
-      </c>
-      <c r="M124">
+      <c r="Q124">
+        <v>25.0</v>
+      </c>
+      <c r="R124">
         <v>45.2</v>
       </c>
-      <c r="N124">
+      <c r="S124">
         <v>1</v>
       </c>
     </row>
@@ -4928,16 +6362,25 @@
       <c r="H125">
         <v>6.9</v>
       </c>
-      <c r="J125">
+      <c r="I125">
         <v>79.2</v>
       </c>
+      <c r="K125">
+        <v>30.0</v>
+      </c>
       <c r="L125">
+        <v>0.0</v>
+      </c>
+      <c r="O125">
+        <v>79.2</v>
+      </c>
+      <c r="Q125">
         <v>30.0</v>
       </c>
-      <c r="M125">
+      <c r="R125">
         <v>44.1</v>
       </c>
-      <c r="N125">
+      <c r="S125">
         <v>1</v>
       </c>
     </row>
@@ -4973,18 +6416,33 @@
         <v>31.3</v>
       </c>
       <c r="I126">
+        <v>59.9</v>
+      </c>
+      <c r="J126">
+        <v>0.0</v>
+      </c>
+      <c r="K126">
+        <v>35.0</v>
+      </c>
+      <c r="L126">
+        <v>0.0</v>
+      </c>
+      <c r="M126">
         <v>1.2</v>
       </c>
-      <c r="J126">
+      <c r="N126">
+        <v>1.2</v>
+      </c>
+      <c r="O126">
         <v>59.9</v>
       </c>
-      <c r="L126">
+      <c r="Q126">
         <v>35.0</v>
       </c>
-      <c r="M126">
+      <c r="R126">
         <v>51.1</v>
       </c>
-      <c r="N126">
+      <c r="S126">
         <v>1</v>
       </c>
     </row>
@@ -5020,15 +6478,27 @@
         <v>84.0</v>
       </c>
       <c r="I127">
+        <v>7.5</v>
+      </c>
+      <c r="J127">
+        <v>0.0</v>
+      </c>
+      <c r="L127">
+        <v>2.5</v>
+      </c>
+      <c r="M127">
         <v>6.2</v>
       </c>
-      <c r="J127">
+      <c r="N127">
+        <v>6.2</v>
+      </c>
+      <c r="O127">
         <v>10.0</v>
       </c>
-      <c r="K127">
-        <v>25.0</v>
-      </c>
-      <c r="N127">
+      <c r="P127">
+        <v>25.0</v>
+      </c>
+      <c r="S127">
         <v>0</v>
       </c>
     </row>
@@ -5064,18 +6534,33 @@
         <v>13.2</v>
       </c>
       <c r="I128">
-        <v>0.0</v>
+        <v>28.6</v>
       </c>
       <c r="J128">
+        <v>0.0</v>
+      </c>
+      <c r="K128">
+        <v>25.0</v>
+      </c>
+      <c r="L128">
+        <v>0.0</v>
+      </c>
+      <c r="M128">
+        <v>0.0</v>
+      </c>
+      <c r="N128">
+        <v>0.0</v>
+      </c>
+      <c r="O128">
         <v>28.6</v>
       </c>
-      <c r="L128">
-        <v>25.0</v>
-      </c>
-      <c r="M128">
+      <c r="Q128">
+        <v>25.0</v>
+      </c>
+      <c r="R128">
         <v>25.1</v>
       </c>
-      <c r="N128">
+      <c r="S128">
         <v>1</v>
       </c>
     </row>
@@ -5111,18 +6596,33 @@
         <v>18.2</v>
       </c>
       <c r="I129">
-        <v>0.0</v>
+        <v>49.5</v>
       </c>
       <c r="J129">
+        <v>0.0</v>
+      </c>
+      <c r="K129">
+        <v>20.0</v>
+      </c>
+      <c r="L129">
+        <v>0.0</v>
+      </c>
+      <c r="M129">
+        <v>0.0</v>
+      </c>
+      <c r="N129">
+        <v>0.0</v>
+      </c>
+      <c r="O129">
         <v>49.5</v>
       </c>
-      <c r="L129">
+      <c r="Q129">
         <v>20.0</v>
       </c>
-      <c r="M129">
+      <c r="R129">
         <v>64.9</v>
       </c>
-      <c r="N129">
+      <c r="S129">
         <v>1</v>
       </c>
     </row>
@@ -5158,21 +6658,36 @@
         <v>16.7</v>
       </c>
       <c r="I130">
+        <v>69.3</v>
+      </c>
+      <c r="J130">
+        <v>0.0</v>
+      </c>
+      <c r="K130">
+        <v>25.0</v>
+      </c>
+      <c r="L130">
+        <v>0.0</v>
+      </c>
+      <c r="M130">
         <v>35.0</v>
       </c>
-      <c r="J130">
+      <c r="N130">
+        <v>35.0</v>
+      </c>
+      <c r="O130">
         <v>69.3</v>
       </c>
-      <c r="K130">
+      <c r="P130">
         <v>17.5</v>
       </c>
-      <c r="L130">
-        <v>25.0</v>
-      </c>
-      <c r="M130">
+      <c r="Q130">
+        <v>25.0</v>
+      </c>
+      <c r="R130">
         <v>41.9</v>
       </c>
-      <c r="N130">
+      <c r="S130">
         <v>1</v>
       </c>
     </row>
@@ -5207,16 +6722,25 @@
       <c r="H131">
         <v>8.5</v>
       </c>
-      <c r="J131">
+      <c r="I131">
         <v>99.0</v>
       </c>
+      <c r="K131">
+        <v>55.0</v>
+      </c>
       <c r="L131">
+        <v>0.0</v>
+      </c>
+      <c r="O131">
+        <v>99.0</v>
+      </c>
+      <c r="Q131">
         <v>55.0</v>
       </c>
-      <c r="M131">
+      <c r="R131">
         <v>67.6</v>
       </c>
-      <c r="N131">
+      <c r="S131">
         <v>1</v>
       </c>
     </row>
@@ -5251,16 +6775,25 @@
       <c r="H132">
         <v>13.1</v>
       </c>
-      <c r="J132">
+      <c r="I132">
         <v>96.9</v>
       </c>
+      <c r="K132">
+        <v>50.0</v>
+      </c>
       <c r="L132">
+        <v>0.0</v>
+      </c>
+      <c r="O132">
+        <v>96.9</v>
+      </c>
+      <c r="Q132">
         <v>50.0</v>
       </c>
-      <c r="M132">
+      <c r="R132">
         <v>81.5</v>
       </c>
-      <c r="N132">
+      <c r="S132">
         <v>2</v>
       </c>
     </row>
@@ -5296,18 +6829,33 @@
         <v>45.5</v>
       </c>
       <c r="I133">
+        <v>9.2</v>
+      </c>
+      <c r="J133">
+        <v>0.0</v>
+      </c>
+      <c r="K133">
+        <v>10.0</v>
+      </c>
+      <c r="L133">
+        <v>1.7</v>
+      </c>
+      <c r="M133">
         <v>1.0</v>
       </c>
-      <c r="J133">
+      <c r="N133">
+        <v>1.0</v>
+      </c>
+      <c r="O133">
         <v>10.8</v>
       </c>
-      <c r="L133">
+      <c r="Q133">
         <v>20.0</v>
       </c>
-      <c r="M133">
+      <c r="R133">
         <v>55.1</v>
       </c>
-      <c r="N133">
+      <c r="S133">
         <v>1</v>
       </c>
     </row>
@@ -5342,19 +6890,28 @@
       <c r="H134">
         <v>11.0</v>
       </c>
-      <c r="J134">
+      <c r="I134">
+        <v>51.5</v>
+      </c>
+      <c r="K134">
+        <v>20.0</v>
+      </c>
+      <c r="L134">
+        <v>18.0</v>
+      </c>
+      <c r="O134">
         <v>69.6</v>
       </c>
-      <c r="K134">
+      <c r="P134">
         <v>10.0</v>
       </c>
-      <c r="L134">
+      <c r="Q134">
         <v>20.0</v>
       </c>
-      <c r="M134">
+      <c r="R134">
         <v>40.6</v>
       </c>
-      <c r="N134">
+      <c r="S134">
         <v>1</v>
       </c>
     </row>
@@ -5390,18 +6947,33 @@
         <v>21.7</v>
       </c>
       <c r="I135">
-        <v>0.0</v>
+        <v>18.1</v>
       </c>
       <c r="J135">
+        <v>0.0</v>
+      </c>
+      <c r="K135">
+        <v>25.0</v>
+      </c>
+      <c r="L135">
+        <v>0.0</v>
+      </c>
+      <c r="M135">
+        <v>0.0</v>
+      </c>
+      <c r="N135">
+        <v>0.0</v>
+      </c>
+      <c r="O135">
         <v>18.1</v>
       </c>
-      <c r="L135">
-        <v>25.0</v>
-      </c>
-      <c r="M135">
+      <c r="Q135">
+        <v>25.0</v>
+      </c>
+      <c r="R135">
         <v>36.5</v>
       </c>
-      <c r="N135">
+      <c r="S135">
         <v>1</v>
       </c>
     </row>
@@ -5437,15 +7009,27 @@
         <v>76.7</v>
       </c>
       <c r="I136">
+        <v>0.0</v>
+      </c>
+      <c r="J136">
+        <v>0.0</v>
+      </c>
+      <c r="L136">
+        <v>4.1</v>
+      </c>
+      <c r="M136">
         <v>6.8</v>
       </c>
-      <c r="J136">
+      <c r="N136">
+        <v>6.8</v>
+      </c>
+      <c r="O136">
         <v>4.1</v>
       </c>
-      <c r="K136">
+      <c r="P136">
         <v>40.0</v>
       </c>
-      <c r="N136">
+      <c r="S136">
         <v>0</v>
       </c>
     </row>
@@ -5480,13 +7064,22 @@
       <c r="H137">
         <v>13.9</v>
       </c>
-      <c r="J137">
-        <v>25.0</v>
+      <c r="I137">
+        <v>25.0</v>
+      </c>
+      <c r="K137">
+        <v>30.0</v>
       </c>
       <c r="L137">
+        <v>0.0</v>
+      </c>
+      <c r="O137">
+        <v>25.0</v>
+      </c>
+      <c r="Q137">
         <v>30.0</v>
       </c>
-      <c r="N137">
+      <c r="S137">
         <v>0</v>
       </c>
     </row>
@@ -5521,13 +7114,22 @@
       <c r="H138">
         <v>0.0</v>
       </c>
-      <c r="J138">
+      <c r="I138">
+        <v>15.3</v>
+      </c>
+      <c r="K138">
+        <v>20.0</v>
+      </c>
+      <c r="L138">
+        <v>0.5</v>
+      </c>
+      <c r="O138">
         <v>15.8</v>
       </c>
-      <c r="L138">
+      <c r="Q138">
         <v>20.0</v>
       </c>
-      <c r="N138">
+      <c r="S138">
         <v>0</v>
       </c>
     </row>
@@ -5562,16 +7164,25 @@
       <c r="H139">
         <v>10.0</v>
       </c>
-      <c r="J139">
+      <c r="I139">
         <v>26.5</v>
       </c>
+      <c r="K139">
+        <v>30.0</v>
+      </c>
       <c r="L139">
+        <v>0.0</v>
+      </c>
+      <c r="O139">
+        <v>26.5</v>
+      </c>
+      <c r="Q139">
         <v>30.0</v>
       </c>
-      <c r="M139">
+      <c r="R139">
         <v>50.0</v>
       </c>
-      <c r="N139">
+      <c r="S139">
         <v>1</v>
       </c>
     </row>
@@ -5606,16 +7217,25 @@
       <c r="H140">
         <v>9.2</v>
       </c>
-      <c r="J140">
+      <c r="I140">
+        <v>48.0</v>
+      </c>
+      <c r="K140">
+        <v>15.0</v>
+      </c>
+      <c r="L140">
+        <v>1.7</v>
+      </c>
+      <c r="O140">
         <v>49.7</v>
       </c>
-      <c r="L140">
+      <c r="Q140">
         <v>15.0</v>
       </c>
-      <c r="M140">
+      <c r="R140">
         <v>84.9</v>
       </c>
-      <c r="N140">
+      <c r="S140">
         <v>1</v>
       </c>
     </row>
@@ -5651,18 +7271,30 @@
         <v>60.5</v>
       </c>
       <c r="I141">
+        <v>0.0</v>
+      </c>
+      <c r="J141">
+        <v>0.0</v>
+      </c>
+      <c r="L141">
+        <v>41.6</v>
+      </c>
+      <c r="M141">
         <v>73.7</v>
       </c>
-      <c r="J141">
+      <c r="N141">
+        <v>73.7</v>
+      </c>
+      <c r="O141">
         <v>41.6</v>
       </c>
-      <c r="K141">
+      <c r="P141">
         <v>20.0</v>
       </c>
-      <c r="L141">
-        <v>25.0</v>
-      </c>
-      <c r="N141">
+      <c r="Q141">
+        <v>25.0</v>
+      </c>
+      <c r="S141">
         <v>0</v>
       </c>
     </row>
@@ -5698,12 +7330,24 @@
         <v>66.0</v>
       </c>
       <c r="I142">
+        <v>0.0</v>
+      </c>
+      <c r="J142">
+        <v>0.0</v>
+      </c>
+      <c r="L142">
+        <v>1.5</v>
+      </c>
+      <c r="M142">
         <v>2.3</v>
       </c>
-      <c r="J142">
+      <c r="N142">
+        <v>2.3</v>
+      </c>
+      <c r="O142">
         <v>1.5</v>
       </c>
-      <c r="N142">
+      <c r="S142">
         <v>0</v>
       </c>
     </row>
@@ -5738,13 +7382,22 @@
       <c r="H143">
         <v>0.0</v>
       </c>
-      <c r="J143">
+      <c r="I143">
         <v>70.8</v>
       </c>
+      <c r="K143">
+        <v>30.0</v>
+      </c>
       <c r="L143">
+        <v>0.0</v>
+      </c>
+      <c r="O143">
+        <v>70.8</v>
+      </c>
+      <c r="Q143">
         <v>30.0</v>
       </c>
-      <c r="N143">
+      <c r="S143">
         <v>0</v>
       </c>
     </row>
@@ -5780,18 +7433,33 @@
         <v>17.3</v>
       </c>
       <c r="I144">
+        <v>50.0</v>
+      </c>
+      <c r="J144">
+        <v>0.0</v>
+      </c>
+      <c r="K144">
+        <v>25.0</v>
+      </c>
+      <c r="L144">
+        <v>0.0</v>
+      </c>
+      <c r="M144">
         <v>6.1</v>
       </c>
-      <c r="J144">
+      <c r="N144">
+        <v>6.1</v>
+      </c>
+      <c r="O144">
         <v>50.0</v>
       </c>
-      <c r="L144">
-        <v>25.0</v>
-      </c>
-      <c r="M144">
+      <c r="Q144">
+        <v>25.0</v>
+      </c>
+      <c r="R144">
         <v>33.7</v>
       </c>
-      <c r="N144">
+      <c r="S144">
         <v>2</v>
       </c>
     </row>
@@ -5826,13 +7494,19 @@
       <c r="H145">
         <v>0.0</v>
       </c>
-      <c r="J145">
+      <c r="I145">
+        <v>4.2</v>
+      </c>
+      <c r="L145">
+        <v>2.6</v>
+      </c>
+      <c r="O145">
         <v>6.9</v>
       </c>
-      <c r="L145">
+      <c r="Q145">
         <v>30.0</v>
       </c>
-      <c r="N145">
+      <c r="S145">
         <v>0</v>
       </c>
     </row>
@@ -5867,16 +7541,25 @@
       <c r="H146">
         <v>11.5</v>
       </c>
-      <c r="J146">
+      <c r="I146">
         <v>84.0</v>
       </c>
+      <c r="K146">
+        <v>25.0</v>
+      </c>
       <c r="L146">
-        <v>25.0</v>
-      </c>
-      <c r="M146">
+        <v>0.0</v>
+      </c>
+      <c r="O146">
+        <v>84.0</v>
+      </c>
+      <c r="Q146">
+        <v>25.0</v>
+      </c>
+      <c r="R146">
         <v>54.0</v>
       </c>
-      <c r="N146">
+      <c r="S146">
         <v>1</v>
       </c>
     </row>
@@ -5912,18 +7595,33 @@
         <v>19.1</v>
       </c>
       <c r="I147">
+        <v>60.1</v>
+      </c>
+      <c r="J147">
+        <v>0.0</v>
+      </c>
+      <c r="K147">
+        <v>25.0</v>
+      </c>
+      <c r="L147">
+        <v>0.0</v>
+      </c>
+      <c r="M147">
         <v>5.7</v>
       </c>
-      <c r="J147">
+      <c r="N147">
+        <v>5.7</v>
+      </c>
+      <c r="O147">
         <v>60.1</v>
       </c>
-      <c r="L147">
-        <v>25.0</v>
-      </c>
-      <c r="M147">
+      <c r="Q147">
+        <v>25.0</v>
+      </c>
+      <c r="R147">
         <v>54.8</v>
       </c>
-      <c r="N147">
+      <c r="S147">
         <v>1</v>
       </c>
     </row>
@@ -5958,13 +7656,19 @@
       <c r="H148">
         <v>0.0</v>
       </c>
-      <c r="J148">
+      <c r="I148">
+        <v>0.0</v>
+      </c>
+      <c r="L148">
         <v>8.4</v>
       </c>
-      <c r="L148">
+      <c r="O148">
+        <v>8.4</v>
+      </c>
+      <c r="Q148">
         <v>30.0</v>
       </c>
-      <c r="N148">
+      <c r="S148">
         <v>0</v>
       </c>
     </row>
@@ -5999,13 +7703,22 @@
       <c r="H149">
         <v>2.3</v>
       </c>
-      <c r="J149">
+      <c r="I149">
         <v>9.3</v>
       </c>
+      <c r="K149">
+        <v>20.0</v>
+      </c>
       <c r="L149">
+        <v>0.0</v>
+      </c>
+      <c r="O149">
+        <v>9.3</v>
+      </c>
+      <c r="Q149">
         <v>20.0</v>
       </c>
-      <c r="N149">
+      <c r="S149">
         <v>0</v>
       </c>
     </row>
@@ -6040,13 +7753,22 @@
       <c r="H150">
         <v>0.0</v>
       </c>
-      <c r="J150">
+      <c r="I150">
+        <v>6.3</v>
+      </c>
+      <c r="K150">
+        <v>20.0</v>
+      </c>
+      <c r="L150">
+        <v>14.9</v>
+      </c>
+      <c r="O150">
         <v>21.3</v>
       </c>
-      <c r="L150">
-        <v>25.0</v>
-      </c>
-      <c r="N150">
+      <c r="Q150">
+        <v>25.0</v>
+      </c>
+      <c r="S150">
         <v>0</v>
       </c>
     </row>
@@ -6081,13 +7803,22 @@
       <c r="H151">
         <v>0.0</v>
       </c>
-      <c r="J151">
+      <c r="I151">
         <v>19.5</v>
       </c>
+      <c r="K151">
+        <v>20.0</v>
+      </c>
       <c r="L151">
+        <v>0.0</v>
+      </c>
+      <c r="O151">
+        <v>19.5</v>
+      </c>
+      <c r="Q151">
         <v>20.0</v>
       </c>
-      <c r="N151">
+      <c r="S151">
         <v>0</v>
       </c>
     </row>
@@ -6122,13 +7853,19 @@
       <c r="H152">
         <v>97.7</v>
       </c>
-      <c r="I152">
+      <c r="J152">
+        <v>0.0</v>
+      </c>
+      <c r="M152">
         <v>42.9</v>
       </c>
-      <c r="K152">
+      <c r="N152">
+        <v>42.9</v>
+      </c>
+      <c r="P152">
         <v>40.0</v>
       </c>
-      <c r="N152">
+      <c r="S152">
         <v>0</v>
       </c>
     </row>
@@ -6163,16 +7900,25 @@
       <c r="H153">
         <v>9.9</v>
       </c>
-      <c r="J153">
+      <c r="I153">
         <v>72.1</v>
       </c>
+      <c r="K153">
+        <v>25.0</v>
+      </c>
       <c r="L153">
-        <v>25.0</v>
-      </c>
-      <c r="M153">
+        <v>0.0</v>
+      </c>
+      <c r="O153">
+        <v>72.1</v>
+      </c>
+      <c r="Q153">
+        <v>25.0</v>
+      </c>
+      <c r="R153">
         <v>48.3</v>
       </c>
-      <c r="N153">
+      <c r="S153">
         <v>1</v>
       </c>
     </row>
@@ -6207,16 +7953,25 @@
       <c r="H154">
         <v>10.5</v>
       </c>
-      <c r="J154">
+      <c r="I154">
         <v>20.9</v>
       </c>
+      <c r="K154">
+        <v>25.0</v>
+      </c>
       <c r="L154">
-        <v>25.0</v>
-      </c>
-      <c r="M154">
+        <v>0.0</v>
+      </c>
+      <c r="O154">
+        <v>20.9</v>
+      </c>
+      <c r="Q154">
+        <v>25.0</v>
+      </c>
+      <c r="R154">
         <v>54.0</v>
       </c>
-      <c r="N154">
+      <c r="S154">
         <v>1</v>
       </c>
     </row>
@@ -6251,16 +8006,25 @@
       <c r="H155">
         <v>12.6</v>
       </c>
-      <c r="J155">
+      <c r="I155">
+        <v>8.2</v>
+      </c>
+      <c r="K155">
+        <v>10.0</v>
+      </c>
+      <c r="L155">
+        <v>0.7</v>
+      </c>
+      <c r="O155">
         <v>8.9</v>
       </c>
-      <c r="L155">
+      <c r="Q155">
         <v>10.0</v>
       </c>
-      <c r="M155">
+      <c r="R155">
         <v>61.2</v>
       </c>
-      <c r="N155">
+      <c r="S155">
         <v>1</v>
       </c>
     </row>
@@ -6295,16 +8059,25 @@
       <c r="H156">
         <v>10.2</v>
       </c>
-      <c r="J156">
+      <c r="I156">
         <v>26.8</v>
       </c>
+      <c r="K156">
+        <v>20.0</v>
+      </c>
       <c r="L156">
+        <v>0.0</v>
+      </c>
+      <c r="O156">
+        <v>26.8</v>
+      </c>
+      <c r="Q156">
         <v>20.0</v>
       </c>
-      <c r="M156">
+      <c r="R156">
         <v>31.7</v>
       </c>
-      <c r="N156">
+      <c r="S156">
         <v>1</v>
       </c>
     </row>
@@ -6340,12 +8113,24 @@
         <v>60.8</v>
       </c>
       <c r="I157">
+        <v>3.1</v>
+      </c>
+      <c r="J157">
+        <v>0.0</v>
+      </c>
+      <c r="L157">
+        <v>3.1</v>
+      </c>
+      <c r="M157">
         <v>4.0</v>
       </c>
-      <c r="J157">
+      <c r="N157">
+        <v>4.0</v>
+      </c>
+      <c r="O157">
         <v>6.2</v>
       </c>
-      <c r="N157">
+      <c r="S157">
         <v>0</v>
       </c>
     </row>
@@ -6380,19 +8165,28 @@
       <c r="H158">
         <v>17.6</v>
       </c>
-      <c r="J158">
+      <c r="I158">
+        <v>50.7</v>
+      </c>
+      <c r="K158">
+        <v>25.0</v>
+      </c>
+      <c r="L158">
+        <v>6.6</v>
+      </c>
+      <c r="O158">
         <v>57.4</v>
       </c>
-      <c r="K158">
+      <c r="P158">
         <v>10.0</v>
       </c>
-      <c r="L158">
-        <v>25.0</v>
-      </c>
-      <c r="M158">
+      <c r="Q158">
+        <v>25.0</v>
+      </c>
+      <c r="R158">
         <v>35.3</v>
       </c>
-      <c r="N158">
+      <c r="S158">
         <v>1</v>
       </c>
     </row>
@@ -6428,15 +8222,27 @@
         <v>74.5</v>
       </c>
       <c r="I159">
+        <v>0.0</v>
+      </c>
+      <c r="J159">
+        <v>0.0</v>
+      </c>
+      <c r="L159">
+        <v>2.4</v>
+      </c>
+      <c r="M159">
         <v>29.3</v>
       </c>
-      <c r="J159">
+      <c r="N159">
+        <v>29.3</v>
+      </c>
+      <c r="O159">
         <v>2.4</v>
       </c>
-      <c r="K159">
+      <c r="P159">
         <v>50.0</v>
       </c>
-      <c r="N159">
+      <c r="S159">
         <v>0</v>
       </c>
     </row>
@@ -6471,13 +8277,19 @@
       <c r="H160">
         <v>14.8</v>
       </c>
-      <c r="J160">
+      <c r="I160">
+        <v>0.0</v>
+      </c>
+      <c r="L160">
         <v>6.5</v>
       </c>
-      <c r="M160">
+      <c r="O160">
+        <v>6.5</v>
+      </c>
+      <c r="R160">
         <v>90.9</v>
       </c>
-      <c r="N160">
+      <c r="S160">
         <v>1</v>
       </c>
     </row>
@@ -6512,16 +8324,25 @@
       <c r="H161">
         <v>9.3</v>
       </c>
-      <c r="J161">
+      <c r="I161">
         <v>69.2</v>
       </c>
+      <c r="K161">
+        <v>35.0</v>
+      </c>
       <c r="L161">
+        <v>0.0</v>
+      </c>
+      <c r="O161">
+        <v>69.2</v>
+      </c>
+      <c r="Q161">
         <v>35.0</v>
       </c>
-      <c r="M161">
+      <c r="R161">
         <v>48.9</v>
       </c>
-      <c r="N161">
+      <c r="S161">
         <v>1</v>
       </c>
     </row>
@@ -6556,16 +8377,25 @@
       <c r="H162">
         <v>5.0</v>
       </c>
-      <c r="J162">
+      <c r="I162">
         <v>19.7</v>
       </c>
+      <c r="K162">
+        <v>25.0</v>
+      </c>
       <c r="L162">
-        <v>25.0</v>
-      </c>
-      <c r="M162">
+        <v>0.0</v>
+      </c>
+      <c r="O162">
+        <v>19.7</v>
+      </c>
+      <c r="Q162">
+        <v>25.0</v>
+      </c>
+      <c r="R162">
         <v>36.3</v>
       </c>
-      <c r="N162">
+      <c r="S162">
         <v>1</v>
       </c>
     </row>
@@ -6600,16 +8430,25 @@
       <c r="H163">
         <v>11.5</v>
       </c>
-      <c r="J163">
+      <c r="I163">
         <v>80.6</v>
       </c>
+      <c r="K163">
+        <v>40.0</v>
+      </c>
       <c r="L163">
+        <v>0.0</v>
+      </c>
+      <c r="O163">
+        <v>80.6</v>
+      </c>
+      <c r="Q163">
         <v>40.0</v>
       </c>
-      <c r="M163">
+      <c r="R163">
         <v>44.3</v>
       </c>
-      <c r="N163">
+      <c r="S163">
         <v>1</v>
       </c>
     </row>
@@ -6644,16 +8483,25 @@
       <c r="H164">
         <v>10.3</v>
       </c>
-      <c r="J164">
+      <c r="I164">
         <v>42.9</v>
       </c>
+      <c r="K164">
+        <v>25.0</v>
+      </c>
       <c r="L164">
-        <v>25.0</v>
-      </c>
-      <c r="M164">
+        <v>0.0</v>
+      </c>
+      <c r="O164">
+        <v>42.9</v>
+      </c>
+      <c r="Q164">
+        <v>25.0</v>
+      </c>
+      <c r="R164">
         <v>24.5</v>
       </c>
-      <c r="N164">
+      <c r="S164">
         <v>1</v>
       </c>
     </row>
@@ -6689,18 +8537,33 @@
         <v>20.8</v>
       </c>
       <c r="I165">
-        <v>0.0</v>
+        <v>59.0</v>
       </c>
       <c r="J165">
+        <v>0.0</v>
+      </c>
+      <c r="K165">
+        <v>35.0</v>
+      </c>
+      <c r="L165">
+        <v>0.0</v>
+      </c>
+      <c r="M165">
+        <v>0.0</v>
+      </c>
+      <c r="N165">
+        <v>0.0</v>
+      </c>
+      <c r="O165">
         <v>59.0</v>
       </c>
-      <c r="L165">
+      <c r="Q165">
         <v>35.0</v>
       </c>
-      <c r="M165">
+      <c r="R165">
         <v>93.4</v>
       </c>
-      <c r="N165">
+      <c r="S165">
         <v>1</v>
       </c>
     </row>
@@ -6736,18 +8599,33 @@
         <v>27.8</v>
       </c>
       <c r="I166">
-        <v>0.0</v>
+        <v>61.5</v>
       </c>
       <c r="J166">
+        <v>0.0</v>
+      </c>
+      <c r="K166">
+        <v>25.0</v>
+      </c>
+      <c r="L166">
+        <v>0.0</v>
+      </c>
+      <c r="M166">
+        <v>0.0</v>
+      </c>
+      <c r="N166">
+        <v>0.0</v>
+      </c>
+      <c r="O166">
         <v>61.5</v>
       </c>
-      <c r="L166">
-        <v>25.0</v>
-      </c>
-      <c r="M166">
+      <c r="Q166">
+        <v>25.0</v>
+      </c>
+      <c r="R166">
         <v>33.1</v>
       </c>
-      <c r="N166">
+      <c r="S166">
         <v>1</v>
       </c>
     </row>
@@ -6782,10 +8660,16 @@
       <c r="H167">
         <v>0.0</v>
       </c>
-      <c r="J167">
+      <c r="I167">
         <v>5.3</v>
       </c>
-      <c r="N167">
+      <c r="L167">
+        <v>0.0</v>
+      </c>
+      <c r="O167">
+        <v>5.3</v>
+      </c>
+      <c r="S167">
         <v>0</v>
       </c>
     </row>
@@ -6820,13 +8704,22 @@
       <c r="H168">
         <v>13.6</v>
       </c>
-      <c r="J168">
+      <c r="I168">
         <v>24.4</v>
       </c>
+      <c r="K168">
+        <v>30.0</v>
+      </c>
       <c r="L168">
+        <v>0.0</v>
+      </c>
+      <c r="O168">
+        <v>24.4</v>
+      </c>
+      <c r="Q168">
         <v>30.0</v>
       </c>
-      <c r="N168">
+      <c r="S168">
         <v>0</v>
       </c>
     </row>
@@ -6861,16 +8754,25 @@
       <c r="H169">
         <v>19.0</v>
       </c>
-      <c r="J169">
+      <c r="I169">
         <v>18.5</v>
       </c>
+      <c r="K169">
+        <v>25.0</v>
+      </c>
       <c r="L169">
-        <v>25.0</v>
-      </c>
-      <c r="M169">
+        <v>0.0</v>
+      </c>
+      <c r="O169">
+        <v>18.5</v>
+      </c>
+      <c r="Q169">
+        <v>25.0</v>
+      </c>
+      <c r="R169">
         <v>50.3</v>
       </c>
-      <c r="N169">
+      <c r="S169">
         <v>1</v>
       </c>
     </row>
@@ -6905,13 +8807,22 @@
       <c r="H170">
         <v>0.0</v>
       </c>
-      <c r="J170">
+      <c r="I170">
+        <v>11.6</v>
+      </c>
+      <c r="K170">
+        <v>20.0</v>
+      </c>
+      <c r="L170">
+        <v>1.4</v>
+      </c>
+      <c r="O170">
         <v>13.0</v>
       </c>
-      <c r="L170">
+      <c r="Q170">
         <v>20.0</v>
       </c>
-      <c r="N170">
+      <c r="S170">
         <v>0</v>
       </c>
     </row>
@@ -6946,13 +8857,22 @@
       <c r="H171">
         <v>0.0</v>
       </c>
-      <c r="J171">
+      <c r="I171">
         <v>17.4</v>
       </c>
+      <c r="K171">
+        <v>30.0</v>
+      </c>
       <c r="L171">
+        <v>0.0</v>
+      </c>
+      <c r="O171">
+        <v>17.4</v>
+      </c>
+      <c r="Q171">
         <v>30.0</v>
       </c>
-      <c r="N171">
+      <c r="S171">
         <v>0</v>
       </c>
     </row>
@@ -6987,13 +8907,19 @@
       <c r="H172">
         <v>0.0</v>
       </c>
-      <c r="J172">
+      <c r="I172">
+        <v>1.5</v>
+      </c>
+      <c r="L172">
+        <v>30.1</v>
+      </c>
+      <c r="O172">
         <v>31.6</v>
       </c>
-      <c r="L172">
+      <c r="Q172">
         <v>20.0</v>
       </c>
-      <c r="N172">
+      <c r="S172">
         <v>0</v>
       </c>
     </row>
@@ -7028,13 +8954,19 @@
       <c r="H173">
         <v>0.0</v>
       </c>
-      <c r="J173">
+      <c r="I173">
+        <v>5.2</v>
+      </c>
+      <c r="L173">
+        <v>10.4</v>
+      </c>
+      <c r="O173">
         <v>15.6</v>
       </c>
-      <c r="L173">
+      <c r="Q173">
         <v>30.0</v>
       </c>
-      <c r="N173">
+      <c r="S173">
         <v>0</v>
       </c>
     </row>
@@ -7069,10 +9001,16 @@
       <c r="H174">
         <v>98.5</v>
       </c>
-      <c r="I174">
+      <c r="J174">
+        <v>0.0</v>
+      </c>
+      <c r="M174">
         <v>0.8</v>
       </c>
       <c r="N174">
+        <v>0.8</v>
+      </c>
+      <c r="S174">
         <v>0</v>
       </c>
     </row>
@@ -7107,16 +9045,25 @@
       <c r="H175">
         <v>9.2</v>
       </c>
-      <c r="J175">
+      <c r="I175">
         <v>78.8</v>
       </c>
+      <c r="K175">
+        <v>25.0</v>
+      </c>
       <c r="L175">
-        <v>25.0</v>
-      </c>
-      <c r="M175">
+        <v>0.0</v>
+      </c>
+      <c r="O175">
+        <v>78.8</v>
+      </c>
+      <c r="Q175">
+        <v>25.0</v>
+      </c>
+      <c r="R175">
         <v>42.2</v>
       </c>
-      <c r="N175">
+      <c r="S175">
         <v>1</v>
       </c>
     </row>
@@ -7151,16 +9098,25 @@
       <c r="H176">
         <v>10.0</v>
       </c>
-      <c r="J176">
+      <c r="I176">
         <v>29.9</v>
       </c>
+      <c r="K176">
+        <v>35.0</v>
+      </c>
       <c r="L176">
+        <v>0.0</v>
+      </c>
+      <c r="O176">
+        <v>29.9</v>
+      </c>
+      <c r="Q176">
         <v>35.0</v>
       </c>
-      <c r="M176">
+      <c r="R176">
         <v>52.1</v>
       </c>
-      <c r="N176">
+      <c r="S176">
         <v>1</v>
       </c>
     </row>
@@ -7195,13 +9151,22 @@
       <c r="H177">
         <v>0.0</v>
       </c>
-      <c r="J177">
+      <c r="I177">
         <v>13.1</v>
       </c>
+      <c r="K177">
+        <v>35.0</v>
+      </c>
       <c r="L177">
+        <v>0.0</v>
+      </c>
+      <c r="O177">
+        <v>13.1</v>
+      </c>
+      <c r="Q177">
         <v>35.0</v>
       </c>
-      <c r="N177">
+      <c r="S177">
         <v>0</v>
       </c>
     </row>
@@ -7236,16 +9201,25 @@
       <c r="H178">
         <v>5.4</v>
       </c>
-      <c r="J178">
+      <c r="I178">
         <v>94.3</v>
       </c>
+      <c r="K178">
+        <v>25.0</v>
+      </c>
       <c r="L178">
-        <v>25.0</v>
-      </c>
-      <c r="M178">
+        <v>0.0</v>
+      </c>
+      <c r="O178">
+        <v>94.3</v>
+      </c>
+      <c r="Q178">
+        <v>25.0</v>
+      </c>
+      <c r="R178">
         <v>27.9</v>
       </c>
-      <c r="N178">
+      <c r="S178">
         <v>1</v>
       </c>
     </row>
@@ -7281,15 +9255,27 @@
         <v>31.0</v>
       </c>
       <c r="I179">
+        <v>0.0</v>
+      </c>
+      <c r="J179">
+        <v>0.0</v>
+      </c>
+      <c r="L179">
+        <v>52.8</v>
+      </c>
+      <c r="M179">
         <v>22.5</v>
       </c>
-      <c r="J179">
+      <c r="N179">
+        <v>22.5</v>
+      </c>
+      <c r="O179">
         <v>52.8</v>
       </c>
-      <c r="L179">
+      <c r="Q179">
         <v>15.0</v>
       </c>
-      <c r="N179">
+      <c r="S179">
         <v>0</v>
       </c>
     </row>
@@ -7324,13 +9310,19 @@
       <c r="H180">
         <v>10.2</v>
       </c>
-      <c r="J180">
+      <c r="I180">
+        <v>0.0</v>
+      </c>
+      <c r="L180">
         <v>24.6</v>
       </c>
-      <c r="L180">
+      <c r="O180">
+        <v>24.6</v>
+      </c>
+      <c r="Q180">
         <v>22.5</v>
       </c>
-      <c r="N180">
+      <c r="S180">
         <v>0</v>
       </c>
     </row>
@@ -7369,9 +9361,21 @@
         <v>0.0</v>
       </c>
       <c r="J181">
+        <v>0.0</v>
+      </c>
+      <c r="L181">
         <v>1.6</v>
       </c>
+      <c r="M181">
+        <v>0.0</v>
+      </c>
       <c r="N181">
+        <v>0.0</v>
+      </c>
+      <c r="O181">
+        <v>1.6</v>
+      </c>
+      <c r="S181">
         <v>0</v>
       </c>
     </row>
@@ -7406,16 +9410,25 @@
       <c r="H182">
         <v>7.2</v>
       </c>
-      <c r="J182">
+      <c r="I182">
         <v>86.2</v>
       </c>
+      <c r="K182">
+        <v>35.0</v>
+      </c>
       <c r="L182">
+        <v>0.0</v>
+      </c>
+      <c r="O182">
+        <v>86.2</v>
+      </c>
+      <c r="Q182">
         <v>35.0</v>
       </c>
-      <c r="M182">
+      <c r="R182">
         <v>24.3</v>
       </c>
-      <c r="N182">
+      <c r="S182">
         <v>1</v>
       </c>
     </row>
@@ -7450,16 +9463,25 @@
       <c r="H183">
         <v>5.6</v>
       </c>
-      <c r="J183">
+      <c r="I183">
         <v>88.9</v>
       </c>
+      <c r="K183">
+        <v>35.0</v>
+      </c>
       <c r="L183">
+        <v>0.0</v>
+      </c>
+      <c r="O183">
+        <v>88.9</v>
+      </c>
+      <c r="Q183">
         <v>35.0</v>
       </c>
-      <c r="M183">
+      <c r="R183">
         <v>25.6</v>
       </c>
-      <c r="N183">
+      <c r="S183">
         <v>1</v>
       </c>
     </row>
@@ -7494,10 +9516,16 @@
       <c r="H184">
         <v>0.0</v>
       </c>
-      <c r="J184">
+      <c r="I184">
+        <v>4.0</v>
+      </c>
+      <c r="L184">
+        <v>3.2</v>
+      </c>
+      <c r="O184">
         <v>7.3</v>
       </c>
-      <c r="N184">
+      <c r="S184">
         <v>0</v>
       </c>
     </row>
@@ -7532,13 +9560,19 @@
       <c r="H185">
         <v>87.1</v>
       </c>
-      <c r="I185">
+      <c r="J185">
         <v>0.0</v>
       </c>
       <c r="M185">
+        <v>0.0</v>
+      </c>
+      <c r="N185">
+        <v>0.0</v>
+      </c>
+      <c r="R185">
         <v>96.4</v>
       </c>
-      <c r="N185">
+      <c r="S185">
         <v>1</v>
       </c>
     </row>
@@ -7573,13 +9607,19 @@
       <c r="H186">
         <v>100.0</v>
       </c>
-      <c r="I186">
+      <c r="J186">
+        <v>0.0</v>
+      </c>
+      <c r="M186">
         <v>34.7</v>
       </c>
-      <c r="K186">
+      <c r="N186">
+        <v>34.7</v>
+      </c>
+      <c r="P186">
         <v>40.0</v>
       </c>
-      <c r="N186">
+      <c r="S186">
         <v>0</v>
       </c>
     </row>
@@ -7614,16 +9654,25 @@
       <c r="H187">
         <v>22.3</v>
       </c>
-      <c r="J187">
+      <c r="I187">
         <v>19.1</v>
       </c>
+      <c r="K187">
+        <v>25.0</v>
+      </c>
       <c r="L187">
-        <v>25.0</v>
-      </c>
-      <c r="M187">
+        <v>0.0</v>
+      </c>
+      <c r="O187">
+        <v>19.1</v>
+      </c>
+      <c r="Q187">
+        <v>25.0</v>
+      </c>
+      <c r="R187">
         <v>57.4</v>
       </c>
-      <c r="N187">
+      <c r="S187">
         <v>1</v>
       </c>
     </row>
@@ -7658,13 +9707,19 @@
       <c r="H188">
         <v>22.5</v>
       </c>
-      <c r="J188">
+      <c r="I188">
+        <v>0.0</v>
+      </c>
+      <c r="L188">
         <v>16.1</v>
       </c>
-      <c r="L188">
+      <c r="O188">
+        <v>16.1</v>
+      </c>
+      <c r="Q188">
         <v>20.0</v>
       </c>
-      <c r="N188">
+      <c r="S188">
         <v>0</v>
       </c>
     </row>
@@ -7699,13 +9754,19 @@
       <c r="H189">
         <v>0.0</v>
       </c>
-      <c r="J189">
+      <c r="I189">
+        <v>2.5</v>
+      </c>
+      <c r="L189">
+        <v>10.1</v>
+      </c>
+      <c r="O189">
         <v>12.6</v>
       </c>
-      <c r="L189">
+      <c r="Q189">
         <v>10.0</v>
       </c>
-      <c r="N189">
+      <c r="S189">
         <v>0</v>
       </c>
     </row>
@@ -7741,18 +9802,33 @@
         <v>40.7</v>
       </c>
       <c r="I190">
-        <v>0.0</v>
+        <v>44.3</v>
       </c>
       <c r="J190">
+        <v>0.0</v>
+      </c>
+      <c r="K190">
+        <v>25.0</v>
+      </c>
+      <c r="L190">
+        <v>0.0</v>
+      </c>
+      <c r="M190">
+        <v>0.0</v>
+      </c>
+      <c r="N190">
+        <v>0.0</v>
+      </c>
+      <c r="O190">
         <v>44.3</v>
       </c>
-      <c r="L190">
-        <v>25.0</v>
-      </c>
-      <c r="M190">
+      <c r="Q190">
+        <v>25.0</v>
+      </c>
+      <c r="R190">
         <v>42.5</v>
       </c>
-      <c r="N190">
+      <c r="S190">
         <v>1</v>
       </c>
     </row>
@@ -7787,13 +9863,22 @@
       <c r="H191">
         <v>0.0</v>
       </c>
-      <c r="J191">
+      <c r="I191">
         <v>80.4</v>
       </c>
+      <c r="K191">
+        <v>30.0</v>
+      </c>
       <c r="L191">
+        <v>0.0</v>
+      </c>
+      <c r="O191">
+        <v>80.4</v>
+      </c>
+      <c r="Q191">
         <v>30.0</v>
       </c>
-      <c r="N191">
+      <c r="S191">
         <v>0</v>
       </c>
     </row>
@@ -7829,18 +9914,33 @@
         <v>28.6</v>
       </c>
       <c r="I192">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="J192">
+        <v>0.0</v>
+      </c>
+      <c r="K192">
+        <v>30.0</v>
+      </c>
+      <c r="L192">
+        <v>0.0</v>
+      </c>
+      <c r="M192">
+        <v>0.0</v>
+      </c>
+      <c r="N192">
+        <v>0.0</v>
+      </c>
+      <c r="O192">
         <v>100.0</v>
       </c>
-      <c r="L192">
+      <c r="Q192">
         <v>30.0</v>
       </c>
-      <c r="M192">
+      <c r="R192">
         <v>67.7</v>
       </c>
-      <c r="N192">
+      <c r="S192">
         <v>1</v>
       </c>
     </row>
@@ -7875,16 +9975,25 @@
       <c r="H193">
         <v>20.7</v>
       </c>
-      <c r="J193">
+      <c r="I193">
         <v>89.8</v>
       </c>
+      <c r="K193">
+        <v>25.0</v>
+      </c>
       <c r="L193">
-        <v>25.0</v>
-      </c>
-      <c r="M193">
+        <v>0.0</v>
+      </c>
+      <c r="O193">
+        <v>89.8</v>
+      </c>
+      <c r="Q193">
+        <v>25.0</v>
+      </c>
+      <c r="R193">
         <v>69.1</v>
       </c>
-      <c r="N193">
+      <c r="S193">
         <v>1</v>
       </c>
     </row>
@@ -7919,13 +10028,19 @@
       <c r="H194">
         <v>88.3</v>
       </c>
-      <c r="I194">
+      <c r="J194">
+        <v>0.0</v>
+      </c>
+      <c r="M194">
         <v>12.2</v>
       </c>
-      <c r="K194">
+      <c r="N194">
+        <v>12.2</v>
+      </c>
+      <c r="P194">
         <v>50.0</v>
       </c>
-      <c r="N194">
+      <c r="S194">
         <v>0</v>
       </c>
     </row>
@@ -7960,16 +10075,25 @@
       <c r="H195">
         <v>25.2</v>
       </c>
-      <c r="J195">
+      <c r="I195">
         <v>48.2</v>
       </c>
+      <c r="K195">
+        <v>20.0</v>
+      </c>
       <c r="L195">
+        <v>0.0</v>
+      </c>
+      <c r="O195">
+        <v>48.2</v>
+      </c>
+      <c r="Q195">
         <v>20.0</v>
       </c>
-      <c r="M195">
+      <c r="R195">
         <v>74.2</v>
       </c>
-      <c r="N195">
+      <c r="S195">
         <v>1</v>
       </c>
     </row>
@@ -8004,10 +10128,16 @@
       <c r="H196">
         <v>0.0</v>
       </c>
-      <c r="J196">
+      <c r="I196">
+        <v>4.7</v>
+      </c>
+      <c r="L196">
+        <v>0.9</v>
+      </c>
+      <c r="O196">
         <v>5.6</v>
       </c>
-      <c r="N196">
+      <c r="S196">
         <v>0</v>
       </c>
     </row>
@@ -8042,13 +10172,22 @@
       <c r="H197">
         <v>3.7</v>
       </c>
-      <c r="J197">
+      <c r="I197">
         <v>37.9</v>
       </c>
+      <c r="K197">
+        <v>35.0</v>
+      </c>
       <c r="L197">
+        <v>0.0</v>
+      </c>
+      <c r="O197">
+        <v>37.9</v>
+      </c>
+      <c r="Q197">
         <v>35.0</v>
       </c>
-      <c r="N197">
+      <c r="S197">
         <v>0</v>
       </c>
     </row>
@@ -8084,18 +10223,33 @@
         <v>39.6</v>
       </c>
       <c r="I198">
-        <v>0.0</v>
+        <v>23.4</v>
       </c>
       <c r="J198">
+        <v>0.0</v>
+      </c>
+      <c r="K198">
+        <v>15.0</v>
+      </c>
+      <c r="L198">
+        <v>0.0</v>
+      </c>
+      <c r="M198">
+        <v>0.0</v>
+      </c>
+      <c r="N198">
+        <v>0.0</v>
+      </c>
+      <c r="O198">
         <v>23.4</v>
       </c>
-      <c r="L198">
+      <c r="Q198">
         <v>15.0</v>
       </c>
-      <c r="M198">
+      <c r="R198">
         <v>38.1</v>
       </c>
-      <c r="N198">
+      <c r="S198">
         <v>1</v>
       </c>
     </row>
@@ -8130,16 +10284,25 @@
       <c r="H199">
         <v>24.5</v>
       </c>
-      <c r="J199">
+      <c r="I199">
         <v>38.8</v>
       </c>
+      <c r="K199">
+        <v>20.0</v>
+      </c>
       <c r="L199">
+        <v>0.0</v>
+      </c>
+      <c r="O199">
+        <v>38.8</v>
+      </c>
+      <c r="Q199">
         <v>20.0</v>
       </c>
-      <c r="M199">
+      <c r="R199">
         <v>81.1</v>
       </c>
-      <c r="N199">
+      <c r="S199">
         <v>1</v>
       </c>
     </row>
@@ -8174,16 +10337,25 @@
       <c r="H200">
         <v>18.1</v>
       </c>
-      <c r="J200">
+      <c r="I200">
         <v>68.6</v>
       </c>
+      <c r="K200">
+        <v>35.0</v>
+      </c>
       <c r="L200">
+        <v>0.0</v>
+      </c>
+      <c r="O200">
+        <v>68.6</v>
+      </c>
+      <c r="Q200">
         <v>35.0</v>
       </c>
-      <c r="M200">
+      <c r="R200">
         <v>73.2</v>
       </c>
-      <c r="N200">
+      <c r="S200">
         <v>2</v>
       </c>
     </row>
@@ -8218,13 +10390,22 @@
       <c r="H201">
         <v>0.0</v>
       </c>
-      <c r="J201">
+      <c r="I201">
         <v>21.2</v>
       </c>
+      <c r="K201">
+        <v>20.0</v>
+      </c>
       <c r="L201">
+        <v>0.0</v>
+      </c>
+      <c r="O201">
+        <v>21.2</v>
+      </c>
+      <c r="Q201">
         <v>20.0</v>
       </c>
-      <c r="N201">
+      <c r="S201">
         <v>0</v>
       </c>
     </row>
@@ -8259,13 +10440,22 @@
       <c r="H202">
         <v>24.0</v>
       </c>
-      <c r="J202">
+      <c r="I202">
         <v>48.1</v>
       </c>
+      <c r="K202">
+        <v>30.0</v>
+      </c>
       <c r="L202">
+        <v>0.0</v>
+      </c>
+      <c r="O202">
+        <v>48.1</v>
+      </c>
+      <c r="Q202">
         <v>30.0</v>
       </c>
-      <c r="N202">
+      <c r="S202">
         <v>0</v>
       </c>
     </row>
@@ -8301,12 +10491,24 @@
         <v>64.4</v>
       </c>
       <c r="I203">
+        <v>0.0</v>
+      </c>
+      <c r="J203">
+        <v>0.0</v>
+      </c>
+      <c r="L203">
+        <v>0.0</v>
+      </c>
+      <c r="M203">
         <v>1.5</v>
       </c>
-      <c r="J203">
-        <v>0.0</v>
-      </c>
       <c r="N203">
+        <v>1.5</v>
+      </c>
+      <c r="O203">
+        <v>0.0</v>
+      </c>
+      <c r="S203">
         <v>0</v>
       </c>
     </row>
@@ -8341,13 +10543,19 @@
       <c r="H204">
         <v>78.8</v>
       </c>
-      <c r="I204">
+      <c r="J204">
+        <v>0.0</v>
+      </c>
+      <c r="M204">
         <v>35.4</v>
       </c>
-      <c r="K204">
+      <c r="N204">
+        <v>35.4</v>
+      </c>
+      <c r="P204">
         <v>50.0</v>
       </c>
-      <c r="N204">
+      <c r="S204">
         <v>0</v>
       </c>
     </row>
@@ -8382,16 +10590,22 @@
       <c r="H205">
         <v>16.3</v>
       </c>
-      <c r="J205">
+      <c r="I205">
+        <v>0.0</v>
+      </c>
+      <c r="L205">
         <v>19.5</v>
       </c>
-      <c r="K205">
+      <c r="O205">
+        <v>19.5</v>
+      </c>
+      <c r="P205">
         <v>15.0</v>
       </c>
-      <c r="L205">
+      <c r="Q205">
         <v>20.0</v>
       </c>
-      <c r="N205">
+      <c r="S205">
         <v>0</v>
       </c>
     </row>
@@ -8427,18 +10641,33 @@
         <v>36.9</v>
       </c>
       <c r="I206">
+        <v>44.6</v>
+      </c>
+      <c r="J206">
+        <v>0.0</v>
+      </c>
+      <c r="K206">
+        <v>25.0</v>
+      </c>
+      <c r="L206">
+        <v>7.7</v>
+      </c>
+      <c r="M206">
         <v>13.2</v>
       </c>
-      <c r="J206">
+      <c r="N206">
+        <v>13.2</v>
+      </c>
+      <c r="O206">
         <v>52.3</v>
       </c>
-      <c r="L206">
-        <v>25.0</v>
-      </c>
-      <c r="M206">
+      <c r="Q206">
+        <v>25.0</v>
+      </c>
+      <c r="R206">
         <v>63.5</v>
       </c>
-      <c r="N206">
+      <c r="S206">
         <v>2</v>
       </c>
     </row>
@@ -8474,18 +10703,30 @@
         <v>29.1</v>
       </c>
       <c r="I207">
+        <v>0.0</v>
+      </c>
+      <c r="J207">
+        <v>0.0</v>
+      </c>
+      <c r="L207">
+        <v>17.8</v>
+      </c>
+      <c r="M207">
         <v>40.0</v>
       </c>
-      <c r="J207">
+      <c r="N207">
+        <v>40.0</v>
+      </c>
+      <c r="O207">
         <v>17.8</v>
       </c>
-      <c r="K207">
-        <v>25.0</v>
-      </c>
-      <c r="L207">
+      <c r="P207">
+        <v>25.0</v>
+      </c>
+      <c r="Q207">
         <v>20.0</v>
       </c>
-      <c r="N207">
+      <c r="S207">
         <v>0</v>
       </c>
     </row>
@@ -8521,15 +10762,30 @@
         <v>66.7</v>
       </c>
       <c r="I208">
-        <v>0.0</v>
+        <v>52.9</v>
       </c>
       <c r="J208">
+        <v>0.0</v>
+      </c>
+      <c r="K208">
+        <v>30.0</v>
+      </c>
+      <c r="L208">
+        <v>0.0</v>
+      </c>
+      <c r="M208">
+        <v>0.0</v>
+      </c>
+      <c r="N208">
+        <v>0.0</v>
+      </c>
+      <c r="O208">
         <v>52.9</v>
       </c>
-      <c r="L208">
+      <c r="Q208">
         <v>30.0</v>
       </c>
-      <c r="N208">
+      <c r="S208">
         <v>0</v>
       </c>
     </row>
@@ -8564,16 +10820,25 @@
       <c r="H209">
         <v>24.5</v>
       </c>
-      <c r="J209">
+      <c r="I209">
         <v>33.8</v>
       </c>
+      <c r="K209">
+        <v>25.0</v>
+      </c>
       <c r="L209">
-        <v>25.0</v>
-      </c>
-      <c r="M209">
+        <v>0.0</v>
+      </c>
+      <c r="O209">
+        <v>33.8</v>
+      </c>
+      <c r="Q209">
+        <v>25.0</v>
+      </c>
+      <c r="R209">
         <v>65.7</v>
       </c>
-      <c r="N209">
+      <c r="S209">
         <v>1</v>
       </c>
     </row>
@@ -8608,16 +10873,25 @@
       <c r="H210">
         <v>10.9</v>
       </c>
-      <c r="J210">
+      <c r="I210">
         <v>75.6</v>
       </c>
+      <c r="K210">
+        <v>25.0</v>
+      </c>
       <c r="L210">
-        <v>25.0</v>
-      </c>
-      <c r="M210">
+        <v>0.0</v>
+      </c>
+      <c r="O210">
+        <v>75.6</v>
+      </c>
+      <c r="Q210">
+        <v>25.0</v>
+      </c>
+      <c r="R210">
         <v>28.7</v>
       </c>
-      <c r="N210">
+      <c r="S210">
         <v>1</v>
       </c>
     </row>
@@ -8652,13 +10926,19 @@
       <c r="H211">
         <v>0.0</v>
       </c>
-      <c r="J211">
+      <c r="I211">
+        <v>4.0</v>
+      </c>
+      <c r="L211">
+        <v>21.8</v>
+      </c>
+      <c r="O211">
         <v>25.7</v>
       </c>
-      <c r="L211">
-        <v>25.0</v>
-      </c>
-      <c r="N211">
+      <c r="Q211">
+        <v>25.0</v>
+      </c>
+      <c r="S211">
         <v>0</v>
       </c>
     </row>
@@ -8693,16 +10973,25 @@
       <c r="H212">
         <v>23.8</v>
       </c>
-      <c r="J212">
+      <c r="I212">
         <v>23.4</v>
       </c>
+      <c r="K212">
+        <v>15.0</v>
+      </c>
       <c r="L212">
+        <v>0.0</v>
+      </c>
+      <c r="O212">
+        <v>23.4</v>
+      </c>
+      <c r="Q212">
         <v>15.0</v>
       </c>
-      <c r="M212">
+      <c r="R212">
         <v>87.4</v>
       </c>
-      <c r="N212">
+      <c r="S212">
         <v>1</v>
       </c>
     </row>
@@ -8737,16 +11026,25 @@
       <c r="H213">
         <v>17.8</v>
       </c>
-      <c r="J213">
+      <c r="I213">
+        <v>67.5</v>
+      </c>
+      <c r="K213">
+        <v>35.0</v>
+      </c>
+      <c r="L213">
+        <v>7.2</v>
+      </c>
+      <c r="O213">
         <v>74.7</v>
       </c>
-      <c r="L213">
+      <c r="Q213">
         <v>35.0</v>
       </c>
-      <c r="M213">
+      <c r="R213">
         <v>85.1</v>
       </c>
-      <c r="N213">
+      <c r="S213">
         <v>1</v>
       </c>
     </row>
@@ -8781,16 +11079,25 @@
       <c r="H214">
         <v>10.9</v>
       </c>
-      <c r="J214">
+      <c r="I214">
         <v>20.0</v>
       </c>
+      <c r="K214">
+        <v>30.0</v>
+      </c>
       <c r="L214">
+        <v>0.0</v>
+      </c>
+      <c r="O214">
+        <v>20.0</v>
+      </c>
+      <c r="Q214">
         <v>30.0</v>
       </c>
-      <c r="M214">
+      <c r="R214">
         <v>39.1</v>
       </c>
-      <c r="N214">
+      <c r="S214">
         <v>1</v>
       </c>
     </row>
@@ -8825,16 +11132,25 @@
       <c r="H215">
         <v>13.0</v>
       </c>
-      <c r="J215">
+      <c r="I215">
+        <v>55.2</v>
+      </c>
+      <c r="K215">
+        <v>30.0</v>
+      </c>
+      <c r="L215">
+        <v>1.1</v>
+      </c>
+      <c r="O215">
         <v>56.3</v>
       </c>
-      <c r="L215">
+      <c r="Q215">
         <v>30.0</v>
       </c>
-      <c r="M215">
+      <c r="R215">
         <v>99.5</v>
       </c>
-      <c r="N215">
+      <c r="S215">
         <v>1</v>
       </c>
     </row>
@@ -8869,16 +11185,25 @@
       <c r="H216">
         <v>24.0</v>
       </c>
-      <c r="J216">
+      <c r="I216">
         <v>69.7</v>
       </c>
+      <c r="K216">
+        <v>25.0</v>
+      </c>
       <c r="L216">
-        <v>25.0</v>
-      </c>
-      <c r="M216">
+        <v>0.0</v>
+      </c>
+      <c r="O216">
+        <v>69.7</v>
+      </c>
+      <c r="Q216">
+        <v>25.0</v>
+      </c>
+      <c r="R216">
         <v>55.2</v>
       </c>
-      <c r="N216">
+      <c r="S216">
         <v>1</v>
       </c>
     </row>
@@ -8913,13 +11238,19 @@
       <c r="H217">
         <v>99.0</v>
       </c>
-      <c r="I217">
+      <c r="J217">
+        <v>0.0</v>
+      </c>
+      <c r="M217">
         <v>29.2</v>
       </c>
-      <c r="K217">
+      <c r="N217">
+        <v>29.2</v>
+      </c>
+      <c r="P217">
         <v>45.0</v>
       </c>
-      <c r="N217">
+      <c r="S217">
         <v>0</v>
       </c>
     </row>
@@ -8954,10 +11285,16 @@
       <c r="H218">
         <v>0.0</v>
       </c>
-      <c r="J218">
+      <c r="I218">
+        <v>2.1</v>
+      </c>
+      <c r="L218">
+        <v>4.2</v>
+      </c>
+      <c r="O218">
         <v>6.3</v>
       </c>
-      <c r="N218">
+      <c r="S218">
         <v>0</v>
       </c>
     </row>
@@ -8993,21 +11330,36 @@
         <v>32.6</v>
       </c>
       <c r="I219">
+        <v>23.4</v>
+      </c>
+      <c r="J219">
+        <v>0.0</v>
+      </c>
+      <c r="K219">
+        <v>12.5</v>
+      </c>
+      <c r="L219">
+        <v>0.0</v>
+      </c>
+      <c r="M219">
         <v>51.6</v>
       </c>
-      <c r="J219">
+      <c r="N219">
+        <v>51.6</v>
+      </c>
+      <c r="O219">
         <v>23.4</v>
       </c>
-      <c r="K219">
+      <c r="P219">
         <v>10.0</v>
       </c>
-      <c r="L219">
+      <c r="Q219">
         <v>12.5</v>
       </c>
-      <c r="M219">
+      <c r="R219">
         <v>74.9</v>
       </c>
-      <c r="N219">
+      <c r="S219">
         <v>1</v>
       </c>
     </row>
@@ -9042,10 +11394,16 @@
       <c r="H220">
         <v>0.0</v>
       </c>
-      <c r="J220">
+      <c r="I220">
+        <v>0.0</v>
+      </c>
+      <c r="L220">
         <v>6.4</v>
       </c>
-      <c r="N220">
+      <c r="O220">
+        <v>6.4</v>
+      </c>
+      <c r="S220">
         <v>0</v>
       </c>
     </row>
@@ -9080,16 +11438,25 @@
       <c r="H221">
         <v>12.9</v>
       </c>
-      <c r="J221">
+      <c r="I221">
         <v>54.3</v>
       </c>
+      <c r="K221">
+        <v>20.0</v>
+      </c>
       <c r="L221">
+        <v>0.0</v>
+      </c>
+      <c r="O221">
+        <v>54.3</v>
+      </c>
+      <c r="Q221">
         <v>20.0</v>
       </c>
-      <c r="M221">
+      <c r="R221">
         <v>18.6</v>
       </c>
-      <c r="N221">
+      <c r="S221">
         <v>2</v>
       </c>
     </row>
@@ -9124,10 +11491,16 @@
       <c r="H222">
         <v>0.0</v>
       </c>
-      <c r="J222">
-        <v>0.0</v>
-      </c>
-      <c r="N222">
+      <c r="I222">
+        <v>0.0</v>
+      </c>
+      <c r="L222">
+        <v>0.0</v>
+      </c>
+      <c r="O222">
+        <v>0.0</v>
+      </c>
+      <c r="S222">
         <v>0</v>
       </c>
     </row>
@@ -9162,10 +11535,16 @@
       <c r="H223">
         <v>97.8</v>
       </c>
-      <c r="I223">
+      <c r="J223">
+        <v>0.0</v>
+      </c>
+      <c r="M223">
         <v>0.0</v>
       </c>
       <c r="N223">
+        <v>0.0</v>
+      </c>
+      <c r="S223">
         <v>0</v>
       </c>
     </row>
@@ -9200,16 +11579,25 @@
       <c r="H224">
         <v>19.6</v>
       </c>
-      <c r="J224">
+      <c r="I224">
         <v>82.4</v>
       </c>
+      <c r="K224">
+        <v>25.0</v>
+      </c>
       <c r="L224">
-        <v>25.0</v>
-      </c>
-      <c r="M224">
+        <v>0.0</v>
+      </c>
+      <c r="O224">
+        <v>82.4</v>
+      </c>
+      <c r="Q224">
+        <v>25.0</v>
+      </c>
+      <c r="R224">
         <v>51.7</v>
       </c>
-      <c r="N224">
+      <c r="S224">
         <v>1</v>
       </c>
     </row>
@@ -9244,13 +11632,19 @@
       <c r="H225">
         <v>81.5</v>
       </c>
-      <c r="I225">
+      <c r="J225">
+        <v>0.0</v>
+      </c>
+      <c r="M225">
         <v>18.7</v>
       </c>
-      <c r="K225">
-        <v>25.0</v>
-      </c>
       <c r="N225">
+        <v>18.7</v>
+      </c>
+      <c r="P225">
+        <v>25.0</v>
+      </c>
+      <c r="S225">
         <v>0</v>
       </c>
     </row>
@@ -9285,16 +11679,25 @@
       <c r="H226">
         <v>22.8</v>
       </c>
-      <c r="J226">
+      <c r="I226">
         <v>33.8</v>
       </c>
+      <c r="K226">
+        <v>20.0</v>
+      </c>
       <c r="L226">
+        <v>0.0</v>
+      </c>
+      <c r="O226">
+        <v>33.8</v>
+      </c>
+      <c r="Q226">
         <v>20.0</v>
       </c>
-      <c r="M226">
+      <c r="R226">
         <v>111.9</v>
       </c>
-      <c r="N226">
+      <c r="S226">
         <v>1</v>
       </c>
     </row>
@@ -9329,16 +11732,25 @@
       <c r="H227">
         <v>26.4</v>
       </c>
-      <c r="J227">
+      <c r="I227">
         <v>41.8</v>
       </c>
+      <c r="K227">
+        <v>40.0</v>
+      </c>
       <c r="L227">
+        <v>0.0</v>
+      </c>
+      <c r="O227">
+        <v>41.8</v>
+      </c>
+      <c r="Q227">
         <v>40.0</v>
       </c>
-      <c r="M227">
+      <c r="R227">
         <v>48.4</v>
       </c>
-      <c r="N227">
+      <c r="S227">
         <v>2</v>
       </c>
     </row>
@@ -9374,18 +11786,33 @@
         <v>42.9</v>
       </c>
       <c r="I228">
-        <v>0.0</v>
+        <v>19.2</v>
       </c>
       <c r="J228">
+        <v>0.0</v>
+      </c>
+      <c r="K228">
+        <v>25.0</v>
+      </c>
+      <c r="L228">
+        <v>0.0</v>
+      </c>
+      <c r="M228">
+        <v>0.0</v>
+      </c>
+      <c r="N228">
+        <v>0.0</v>
+      </c>
+      <c r="O228">
         <v>19.2</v>
       </c>
-      <c r="L228">
-        <v>25.0</v>
-      </c>
-      <c r="M228">
+      <c r="Q228">
+        <v>25.0</v>
+      </c>
+      <c r="R228">
         <v>25.5</v>
       </c>
-      <c r="N228">
+      <c r="S228">
         <v>2</v>
       </c>
     </row>
@@ -9420,13 +11847,19 @@
       <c r="H229">
         <v>0.0</v>
       </c>
-      <c r="J229">
+      <c r="I229">
+        <v>8.8</v>
+      </c>
+      <c r="L229">
+        <v>17.6</v>
+      </c>
+      <c r="O229">
         <v>26.4</v>
       </c>
-      <c r="L229">
+      <c r="Q229">
         <v>35.0</v>
       </c>
-      <c r="N229">
+      <c r="S229">
         <v>0</v>
       </c>
     </row>
@@ -9461,13 +11894,19 @@
       <c r="H230">
         <v>98.9</v>
       </c>
-      <c r="I230">
+      <c r="J230">
+        <v>0.0</v>
+      </c>
+      <c r="M230">
         <v>24.4</v>
       </c>
-      <c r="K230">
+      <c r="N230">
+        <v>24.4</v>
+      </c>
+      <c r="P230">
         <v>50.0</v>
       </c>
-      <c r="N230">
+      <c r="S230">
         <v>0</v>
       </c>
     </row>
@@ -9502,10 +11941,16 @@
       <c r="H231">
         <v>0.0</v>
       </c>
-      <c r="J231">
+      <c r="I231">
+        <v>0.0</v>
+      </c>
+      <c r="L231">
         <v>2.2</v>
       </c>
-      <c r="N231">
+      <c r="O231">
+        <v>2.2</v>
+      </c>
+      <c r="S231">
         <v>0</v>
       </c>
     </row>
@@ -9540,13 +11985,19 @@
       <c r="H232">
         <v>27.5</v>
       </c>
-      <c r="J232">
+      <c r="I232">
         <v>15.2</v>
       </c>
-      <c r="M232">
+      <c r="L232">
+        <v>0.0</v>
+      </c>
+      <c r="O232">
+        <v>15.2</v>
+      </c>
+      <c r="R232">
         <v>86.0</v>
       </c>
-      <c r="N232">
+      <c r="S232">
         <v>1</v>
       </c>
     </row>
@@ -9581,16 +12032,25 @@
       <c r="H233">
         <v>17.8</v>
       </c>
-      <c r="J233">
+      <c r="I233">
         <v>21.6</v>
       </c>
       <c r="K233">
         <v>20.0</v>
       </c>
       <c r="L233">
+        <v>0.0</v>
+      </c>
+      <c r="O233">
+        <v>21.6</v>
+      </c>
+      <c r="P233">
         <v>20.0</v>
       </c>
-      <c r="N233">
+      <c r="Q233">
+        <v>20.0</v>
+      </c>
+      <c r="S233">
         <v>0</v>
       </c>
     </row>
@@ -9626,21 +12086,36 @@
         <v>52.2</v>
       </c>
       <c r="I234">
+        <v>46.5</v>
+      </c>
+      <c r="J234">
+        <v>0.0</v>
+      </c>
+      <c r="K234">
+        <v>25.0</v>
+      </c>
+      <c r="L234">
+        <v>2.3</v>
+      </c>
+      <c r="M234">
         <v>29.8</v>
       </c>
-      <c r="J234">
+      <c r="N234">
+        <v>29.8</v>
+      </c>
+      <c r="O234">
         <v>48.8</v>
       </c>
-      <c r="K234">
+      <c r="P234">
         <v>15.0</v>
       </c>
-      <c r="L234">
-        <v>25.0</v>
-      </c>
-      <c r="M234">
+      <c r="Q234">
+        <v>25.0</v>
+      </c>
+      <c r="R234">
         <v>113.5</v>
       </c>
-      <c r="N234">
+      <c r="S234">
         <v>1</v>
       </c>
     </row>
@@ -9675,16 +12150,25 @@
       <c r="H235">
         <v>31.5</v>
       </c>
-      <c r="J235">
+      <c r="I235">
         <v>39.3</v>
       </c>
+      <c r="K235">
+        <v>15.0</v>
+      </c>
       <c r="L235">
+        <v>0.0</v>
+      </c>
+      <c r="O235">
+        <v>39.3</v>
+      </c>
+      <c r="Q235">
         <v>15.0</v>
       </c>
-      <c r="M235">
+      <c r="R235">
         <v>47.5</v>
       </c>
-      <c r="N235">
+      <c r="S235">
         <v>1</v>
       </c>
     </row>
@@ -9720,18 +12204,33 @@
         <v>50.6</v>
       </c>
       <c r="I236">
+        <v>56.8</v>
+      </c>
+      <c r="J236">
+        <v>0.0</v>
+      </c>
+      <c r="K236">
+        <v>25.0</v>
+      </c>
+      <c r="L236">
+        <v>11.4</v>
+      </c>
+      <c r="M236">
         <v>15.6</v>
       </c>
-      <c r="J236">
+      <c r="N236">
+        <v>15.6</v>
+      </c>
+      <c r="O236">
         <v>68.2</v>
       </c>
-      <c r="L236">
-        <v>25.0</v>
-      </c>
-      <c r="M236">
+      <c r="Q236">
+        <v>25.0</v>
+      </c>
+      <c r="R236">
         <v>95.3</v>
       </c>
-      <c r="N236">
+      <c r="S236">
         <v>2</v>
       </c>
     </row>
@@ -9766,13 +12265,22 @@
       <c r="H237">
         <v>0.0</v>
       </c>
-      <c r="J237">
+      <c r="I237">
         <v>78.4</v>
       </c>
+      <c r="K237">
+        <v>25.0</v>
+      </c>
       <c r="L237">
-        <v>25.0</v>
-      </c>
-      <c r="N237">
+        <v>0.0</v>
+      </c>
+      <c r="O237">
+        <v>78.4</v>
+      </c>
+      <c r="Q237">
+        <v>25.0</v>
+      </c>
+      <c r="S237">
         <v>0</v>
       </c>
     </row>
@@ -9807,13 +12315,19 @@
       <c r="H238">
         <v>0.0</v>
       </c>
-      <c r="J238">
+      <c r="I238">
+        <v>0.0</v>
+      </c>
+      <c r="L238">
         <v>63.6</v>
       </c>
-      <c r="L238">
+      <c r="O238">
+        <v>63.6</v>
+      </c>
+      <c r="Q238">
         <v>20.0</v>
       </c>
-      <c r="N238">
+      <c r="S238">
         <v>0</v>
       </c>
     </row>
@@ -9848,16 +12362,25 @@
       <c r="H239">
         <v>27.3</v>
       </c>
-      <c r="J239">
+      <c r="I239">
         <v>43.8</v>
       </c>
+      <c r="K239">
+        <v>50.0</v>
+      </c>
       <c r="L239">
+        <v>0.0</v>
+      </c>
+      <c r="O239">
+        <v>43.8</v>
+      </c>
+      <c r="Q239">
         <v>50.0</v>
       </c>
-      <c r="M239">
+      <c r="R239">
         <v>71.4</v>
       </c>
-      <c r="N239">
+      <c r="S239">
         <v>1</v>
       </c>
     </row>
@@ -9892,16 +12415,25 @@
       <c r="H240">
         <v>20.5</v>
       </c>
-      <c r="J240">
+      <c r="I240">
         <v>51.4</v>
       </c>
+      <c r="K240">
+        <v>25.0</v>
+      </c>
       <c r="L240">
-        <v>25.0</v>
-      </c>
-      <c r="M240">
+        <v>0.0</v>
+      </c>
+      <c r="O240">
+        <v>51.4</v>
+      </c>
+      <c r="Q240">
+        <v>25.0</v>
+      </c>
+      <c r="R240">
         <v>66.8</v>
       </c>
-      <c r="N240">
+      <c r="S240">
         <v>1</v>
       </c>
     </row>
@@ -9936,13 +12468,19 @@
       <c r="H241">
         <v>90.8</v>
       </c>
-      <c r="I241">
+      <c r="J241">
+        <v>0.0</v>
+      </c>
+      <c r="M241">
         <v>48.1</v>
       </c>
-      <c r="K241">
+      <c r="N241">
+        <v>48.1</v>
+      </c>
+      <c r="P241">
         <v>40.0</v>
       </c>
-      <c r="N241">
+      <c r="S241">
         <v>0</v>
       </c>
     </row>
@@ -9978,15 +12516,27 @@
         <v>62.4</v>
       </c>
       <c r="I242">
+        <v>6.2</v>
+      </c>
+      <c r="J242">
+        <v>0.0</v>
+      </c>
+      <c r="L242">
+        <v>0.0</v>
+      </c>
+      <c r="M242">
         <v>7.5</v>
       </c>
-      <c r="J242">
+      <c r="N242">
+        <v>7.5</v>
+      </c>
+      <c r="O242">
         <v>6.2</v>
       </c>
-      <c r="M242">
+      <c r="R242">
         <v>53.3</v>
       </c>
-      <c r="N242">
+      <c r="S242">
         <v>1</v>
       </c>
     </row>
@@ -10021,16 +12571,25 @@
       <c r="H243">
         <v>16.7</v>
       </c>
-      <c r="J243">
+      <c r="I243">
         <v>24.3</v>
       </c>
+      <c r="K243">
+        <v>50.0</v>
+      </c>
       <c r="L243">
+        <v>0.0</v>
+      </c>
+      <c r="O243">
+        <v>24.3</v>
+      </c>
+      <c r="Q243">
         <v>50.0</v>
       </c>
-      <c r="M243">
+      <c r="R243">
         <v>51.3</v>
       </c>
-      <c r="N243">
+      <c r="S243">
         <v>1</v>
       </c>
     </row>
@@ -10065,13 +12624,19 @@
       <c r="H244">
         <v>0.0</v>
       </c>
-      <c r="J244">
+      <c r="I244">
+        <v>0.0</v>
+      </c>
+      <c r="L244">
         <v>25.3</v>
       </c>
-      <c r="L244">
+      <c r="O244">
+        <v>25.3</v>
+      </c>
+      <c r="Q244">
         <v>50.0</v>
       </c>
-      <c r="N244">
+      <c r="S244">
         <v>0</v>
       </c>
     </row>
@@ -10106,10 +12671,16 @@
       <c r="H245">
         <v>98.8</v>
       </c>
-      <c r="I245">
+      <c r="J245">
+        <v>0.0</v>
+      </c>
+      <c r="M245">
         <v>8.5</v>
       </c>
       <c r="N245">
+        <v>8.5</v>
+      </c>
+      <c r="S245">
         <v>0</v>
       </c>
     </row>
@@ -10144,13 +12715,19 @@
       <c r="H246">
         <v>66.3</v>
       </c>
-      <c r="I246">
+      <c r="J246">
+        <v>0.0</v>
+      </c>
+      <c r="M246">
         <v>5.5</v>
       </c>
-      <c r="M246">
+      <c r="N246">
+        <v>5.5</v>
+      </c>
+      <c r="R246">
         <v>86.1</v>
       </c>
-      <c r="N246">
+      <c r="S246">
         <v>2</v>
       </c>
     </row>
@@ -10185,13 +12762,19 @@
       <c r="H247">
         <v>21.7</v>
       </c>
-      <c r="J247">
+      <c r="I247">
         <v>3.1</v>
       </c>
-      <c r="M247">
+      <c r="L247">
+        <v>0.0</v>
+      </c>
+      <c r="O247">
+        <v>3.1</v>
+      </c>
+      <c r="R247">
         <v>26.1</v>
       </c>
-      <c r="N247">
+      <c r="S247">
         <v>1</v>
       </c>
     </row>
@@ -10226,13 +12809,22 @@
       <c r="H248">
         <v>0.0</v>
       </c>
-      <c r="J248">
+      <c r="I248">
+        <v>41.5</v>
+      </c>
+      <c r="K248">
+        <v>30.0</v>
+      </c>
+      <c r="L248">
+        <v>12.2</v>
+      </c>
+      <c r="O248">
         <v>53.7</v>
       </c>
-      <c r="L248">
+      <c r="Q248">
         <v>30.0</v>
       </c>
-      <c r="N248">
+      <c r="S248">
         <v>0</v>
       </c>
     </row>
@@ -10267,16 +12859,25 @@
       <c r="H249">
         <v>18.3</v>
       </c>
-      <c r="J249">
+      <c r="I249">
         <v>86.6</v>
       </c>
+      <c r="K249">
+        <v>50.0</v>
+      </c>
       <c r="L249">
+        <v>0.0</v>
+      </c>
+      <c r="O249">
+        <v>86.6</v>
+      </c>
+      <c r="Q249">
         <v>50.0</v>
       </c>
-      <c r="M249">
+      <c r="R249">
         <v>57.7</v>
       </c>
-      <c r="N249">
+      <c r="S249">
         <v>1</v>
       </c>
     </row>
@@ -10311,16 +12912,22 @@
       <c r="H250">
         <v>19.5</v>
       </c>
-      <c r="J250">
+      <c r="I250">
+        <v>0.0</v>
+      </c>
+      <c r="L250">
         <v>66.7</v>
       </c>
-      <c r="K250">
+      <c r="O250">
+        <v>66.7</v>
+      </c>
+      <c r="P250">
         <v>20.0</v>
       </c>
-      <c r="L250">
+      <c r="Q250">
         <v>20.0</v>
       </c>
-      <c r="N250">
+      <c r="S250">
         <v>0</v>
       </c>
     </row>
@@ -10355,10 +12962,16 @@
       <c r="H251">
         <v>1.2</v>
       </c>
-      <c r="J251">
+      <c r="I251">
         <v>10.0</v>
       </c>
-      <c r="N251">
+      <c r="L251">
+        <v>0.0</v>
+      </c>
+      <c r="O251">
+        <v>10.0</v>
+      </c>
+      <c r="S251">
         <v>0</v>
       </c>
     </row>
@@ -10393,16 +13006,25 @@
       <c r="H252">
         <v>16.2</v>
       </c>
-      <c r="J252">
+      <c r="I252">
         <v>68.7</v>
       </c>
+      <c r="K252">
+        <v>35.0</v>
+      </c>
       <c r="L252">
+        <v>0.0</v>
+      </c>
+      <c r="O252">
+        <v>68.7</v>
+      </c>
+      <c r="Q252">
         <v>35.0</v>
       </c>
-      <c r="M252">
+      <c r="R252">
         <v>37.2</v>
       </c>
-      <c r="N252">
+      <c r="S252">
         <v>1</v>
       </c>
     </row>
@@ -10437,13 +13059,19 @@
       <c r="H253">
         <v>0.0</v>
       </c>
-      <c r="J253">
+      <c r="I253">
+        <v>1.2</v>
+      </c>
+      <c r="L253">
+        <v>65.0</v>
+      </c>
+      <c r="O253">
         <v>66.2</v>
       </c>
-      <c r="L253">
+      <c r="Q253">
         <v>40.0</v>
       </c>
-      <c r="N253">
+      <c r="S253">
         <v>0</v>
       </c>
     </row>
@@ -10478,16 +13106,25 @@
       <c r="H254">
         <v>22.5</v>
       </c>
-      <c r="J254">
+      <c r="I254">
         <v>22.6</v>
       </c>
+      <c r="K254">
+        <v>15.0</v>
+      </c>
       <c r="L254">
+        <v>0.0</v>
+      </c>
+      <c r="O254">
+        <v>22.6</v>
+      </c>
+      <c r="Q254">
         <v>15.0</v>
       </c>
-      <c r="M254">
+      <c r="R254">
         <v>56.1</v>
       </c>
-      <c r="N254">
+      <c r="S254">
         <v>1</v>
       </c>
     </row>
@@ -10522,13 +13159,19 @@
       <c r="H255">
         <v>75.0</v>
       </c>
-      <c r="I255">
+      <c r="J255">
         <v>0.0</v>
       </c>
       <c r="M255">
+        <v>0.0</v>
+      </c>
+      <c r="N255">
+        <v>0.0</v>
+      </c>
+      <c r="R255">
         <v>86.4</v>
       </c>
-      <c r="N255">
+      <c r="S255">
         <v>1</v>
       </c>
     </row>
@@ -10563,16 +13206,25 @@
       <c r="H256">
         <v>27.5</v>
       </c>
-      <c r="J256">
+      <c r="I256">
         <v>37.9</v>
       </c>
+      <c r="K256">
+        <v>25.0</v>
+      </c>
       <c r="L256">
-        <v>25.0</v>
-      </c>
-      <c r="M256">
+        <v>0.0</v>
+      </c>
+      <c r="O256">
+        <v>37.9</v>
+      </c>
+      <c r="Q256">
+        <v>25.0</v>
+      </c>
+      <c r="R256">
         <v>59.1</v>
       </c>
-      <c r="N256">
+      <c r="S256">
         <v>1</v>
       </c>
     </row>
@@ -10607,10 +13259,16 @@
       <c r="H257">
         <v>0.0</v>
       </c>
-      <c r="J257">
+      <c r="I257">
         <v>11.4</v>
       </c>
-      <c r="N257">
+      <c r="L257">
+        <v>0.0</v>
+      </c>
+      <c r="O257">
+        <v>11.4</v>
+      </c>
+      <c r="S257">
         <v>0</v>
       </c>
     </row>
@@ -10645,16 +13303,25 @@
       <c r="H258">
         <v>17.7</v>
       </c>
-      <c r="J258">
+      <c r="I258">
         <v>36.9</v>
       </c>
+      <c r="K258">
+        <v>20.0</v>
+      </c>
       <c r="L258">
+        <v>0.0</v>
+      </c>
+      <c r="O258">
+        <v>36.9</v>
+      </c>
+      <c r="Q258">
         <v>20.0</v>
       </c>
-      <c r="M258">
+      <c r="R258">
         <v>28.6</v>
       </c>
-      <c r="N258">
+      <c r="S258">
         <v>1</v>
       </c>
     </row>
@@ -10689,13 +13356,19 @@
       <c r="H259">
         <v>14.1</v>
       </c>
-      <c r="J259">
+      <c r="I259">
         <v>9.0</v>
       </c>
-      <c r="M259">
+      <c r="L259">
+        <v>0.0</v>
+      </c>
+      <c r="O259">
+        <v>9.0</v>
+      </c>
+      <c r="R259">
         <v>52.5</v>
       </c>
-      <c r="N259">
+      <c r="S259">
         <v>1</v>
       </c>
     </row>
@@ -10736,7 +13409,19 @@
       <c r="J260">
         <v>0.0</v>
       </c>
+      <c r="L260">
+        <v>0.0</v>
+      </c>
+      <c r="M260">
+        <v>0.0</v>
+      </c>
       <c r="N260">
+        <v>0.0</v>
+      </c>
+      <c r="O260">
+        <v>0.0</v>
+      </c>
+      <c r="S260">
         <v>0</v>
       </c>
     </row>
@@ -10771,10 +13456,16 @@
       <c r="H261">
         <v>1.3</v>
       </c>
-      <c r="J261">
+      <c r="I261">
+        <v>0.0</v>
+      </c>
+      <c r="L261">
         <v>11.8</v>
       </c>
-      <c r="N261">
+      <c r="O261">
+        <v>11.8</v>
+      </c>
+      <c r="S261">
         <v>0</v>
       </c>
     </row>
@@ -10809,13 +13500,19 @@
       <c r="H262">
         <v>27.3</v>
       </c>
-      <c r="J262">
+      <c r="I262">
         <v>7.1</v>
       </c>
-      <c r="M262">
+      <c r="L262">
+        <v>0.0</v>
+      </c>
+      <c r="O262">
+        <v>7.1</v>
+      </c>
+      <c r="R262">
         <v>47.9</v>
       </c>
-      <c r="N262">
+      <c r="S262">
         <v>1</v>
       </c>
     </row>
@@ -10850,13 +13547,22 @@
       <c r="H263">
         <v>10.5</v>
       </c>
-      <c r="J263">
+      <c r="I263">
+        <v>98.5</v>
+      </c>
+      <c r="K263">
+        <v>40.0</v>
+      </c>
+      <c r="L263">
+        <v>1.5</v>
+      </c>
+      <c r="O263">
         <v>100.0</v>
       </c>
-      <c r="L263">
+      <c r="Q263">
         <v>40.0</v>
       </c>
-      <c r="N263">
+      <c r="S263">
         <v>0</v>
       </c>
     </row>
@@ -10891,16 +13597,25 @@
       <c r="H264">
         <v>19.7</v>
       </c>
-      <c r="J264">
+      <c r="I264">
         <v>63.9</v>
       </c>
+      <c r="K264">
+        <v>35.0</v>
+      </c>
       <c r="L264">
+        <v>0.0</v>
+      </c>
+      <c r="O264">
+        <v>63.9</v>
+      </c>
+      <c r="Q264">
         <v>35.0</v>
       </c>
-      <c r="M264">
+      <c r="R264">
         <v>48.7</v>
       </c>
-      <c r="N264">
+      <c r="S264">
         <v>1</v>
       </c>
     </row>
@@ -10935,10 +13650,16 @@
       <c r="H265">
         <v>1.3</v>
       </c>
-      <c r="J265">
-        <v>0.0</v>
-      </c>
-      <c r="N265">
+      <c r="I265">
+        <v>0.0</v>
+      </c>
+      <c r="L265">
+        <v>0.0</v>
+      </c>
+      <c r="O265">
+        <v>0.0</v>
+      </c>
+      <c r="S265">
         <v>0</v>
       </c>
     </row>
@@ -10973,16 +13694,25 @@
       <c r="H266">
         <v>10.7</v>
       </c>
-      <c r="J266">
+      <c r="I266">
         <v>61.2</v>
       </c>
+      <c r="K266">
+        <v>20.0</v>
+      </c>
       <c r="L266">
+        <v>0.0</v>
+      </c>
+      <c r="O266">
+        <v>61.2</v>
+      </c>
+      <c r="Q266">
         <v>20.0</v>
       </c>
-      <c r="M266">
+      <c r="R266">
         <v>93.9</v>
       </c>
-      <c r="N266">
+      <c r="S266">
         <v>1</v>
       </c>
     </row>
@@ -11017,16 +13747,25 @@
       <c r="H267">
         <v>13.3</v>
       </c>
-      <c r="J267">
+      <c r="I267">
         <v>32.3</v>
       </c>
+      <c r="K267">
+        <v>25.0</v>
+      </c>
       <c r="L267">
-        <v>25.0</v>
-      </c>
-      <c r="M267">
+        <v>0.0</v>
+      </c>
+      <c r="O267">
+        <v>32.3</v>
+      </c>
+      <c r="Q267">
+        <v>25.0</v>
+      </c>
+      <c r="R267">
         <v>29.9</v>
       </c>
-      <c r="N267">
+      <c r="S267">
         <v>1</v>
       </c>
     </row>
@@ -11061,13 +13800,19 @@
       <c r="H268">
         <v>31.1</v>
       </c>
-      <c r="J268">
+      <c r="I268">
+        <v>0.0</v>
+      </c>
+      <c r="L268">
         <v>7.8</v>
       </c>
-      <c r="M268">
+      <c r="O268">
+        <v>7.8</v>
+      </c>
+      <c r="R268">
         <v>52.7</v>
       </c>
-      <c r="N268">
+      <c r="S268">
         <v>1</v>
       </c>
     </row>
@@ -11102,10 +13847,16 @@
       <c r="H269">
         <v>97.3</v>
       </c>
-      <c r="I269">
+      <c r="J269">
+        <v>0.0</v>
+      </c>
+      <c r="M269">
         <v>1.4</v>
       </c>
       <c r="N269">
+        <v>1.4</v>
+      </c>
+      <c r="S269">
         <v>0</v>
       </c>
     </row>
@@ -11140,16 +13891,25 @@
       <c r="H270">
         <v>17.8</v>
       </c>
-      <c r="J270">
+      <c r="I270">
         <v>61.7</v>
       </c>
+      <c r="K270">
+        <v>25.0</v>
+      </c>
       <c r="L270">
-        <v>25.0</v>
-      </c>
-      <c r="M270">
+        <v>0.0</v>
+      </c>
+      <c r="O270">
+        <v>61.7</v>
+      </c>
+      <c r="Q270">
+        <v>25.0</v>
+      </c>
+      <c r="R270">
         <v>102.5</v>
       </c>
-      <c r="N270">
+      <c r="S270">
         <v>1</v>
       </c>
     </row>
@@ -11184,10 +13944,16 @@
       <c r="H271">
         <v>0.0</v>
       </c>
-      <c r="J271">
-        <v>0.0</v>
-      </c>
-      <c r="N271">
+      <c r="I271">
+        <v>0.0</v>
+      </c>
+      <c r="L271">
+        <v>0.0</v>
+      </c>
+      <c r="O271">
+        <v>0.0</v>
+      </c>
+      <c r="S271">
         <v>0</v>
       </c>
     </row>
@@ -11222,16 +13988,25 @@
       <c r="H272">
         <v>8.3</v>
       </c>
-      <c r="J272">
+      <c r="I272">
         <v>18.2</v>
       </c>
+      <c r="K272">
+        <v>20.0</v>
+      </c>
       <c r="L272">
+        <v>0.0</v>
+      </c>
+      <c r="O272">
+        <v>18.2</v>
+      </c>
+      <c r="Q272">
         <v>20.0</v>
       </c>
-      <c r="M272">
+      <c r="R272">
         <v>64.8</v>
       </c>
-      <c r="N272">
+      <c r="S272">
         <v>1</v>
       </c>
     </row>
@@ -11266,16 +14041,25 @@
       <c r="H273">
         <v>15.3</v>
       </c>
-      <c r="J273">
+      <c r="I273">
         <v>63.9</v>
       </c>
+      <c r="K273">
+        <v>25.0</v>
+      </c>
       <c r="L273">
-        <v>25.0</v>
-      </c>
-      <c r="M273">
+        <v>0.0</v>
+      </c>
+      <c r="O273">
+        <v>63.9</v>
+      </c>
+      <c r="Q273">
+        <v>25.0</v>
+      </c>
+      <c r="R273">
         <v>38.6</v>
       </c>
-      <c r="N273">
+      <c r="S273">
         <v>1</v>
       </c>
     </row>
@@ -11310,10 +14094,16 @@
       <c r="H274">
         <v>0.0</v>
       </c>
-      <c r="J274">
+      <c r="I274">
+        <v>5.6</v>
+      </c>
+      <c r="L274">
+        <v>2.8</v>
+      </c>
+      <c r="O274">
         <v>8.5</v>
       </c>
-      <c r="N274">
+      <c r="S274">
         <v>0</v>
       </c>
     </row>
@@ -11348,16 +14138,25 @@
       <c r="H275">
         <v>37.1</v>
       </c>
-      <c r="J275">
+      <c r="I275">
         <v>50.0</v>
       </c>
+      <c r="K275">
+        <v>35.0</v>
+      </c>
       <c r="L275">
+        <v>0.0</v>
+      </c>
+      <c r="O275">
+        <v>50.0</v>
+      </c>
+      <c r="Q275">
         <v>35.0</v>
       </c>
-      <c r="M275">
+      <c r="R275">
         <v>90.3</v>
       </c>
-      <c r="N275">
+      <c r="S275">
         <v>1</v>
       </c>
     </row>
@@ -11392,16 +14191,25 @@
       <c r="H276">
         <v>10.1</v>
       </c>
-      <c r="J276">
+      <c r="I276">
         <v>83.9</v>
       </c>
+      <c r="K276">
+        <v>25.0</v>
+      </c>
       <c r="L276">
-        <v>25.0</v>
-      </c>
-      <c r="M276">
+        <v>0.0</v>
+      </c>
+      <c r="O276">
+        <v>83.9</v>
+      </c>
+      <c r="Q276">
+        <v>25.0</v>
+      </c>
+      <c r="R276">
         <v>43.7</v>
       </c>
-      <c r="N276">
+      <c r="S276">
         <v>1</v>
       </c>
     </row>
@@ -11436,10 +14244,16 @@
       <c r="H277">
         <v>0.0</v>
       </c>
-      <c r="J277">
+      <c r="I277">
+        <v>5.8</v>
+      </c>
+      <c r="L277">
+        <v>2.9</v>
+      </c>
+      <c r="O277">
         <v>8.7</v>
       </c>
-      <c r="N277">
+      <c r="S277">
         <v>0</v>
       </c>
     </row>
@@ -11474,13 +14288,19 @@
       <c r="H278">
         <v>0.0</v>
       </c>
-      <c r="J278">
+      <c r="I278">
+        <v>10.1</v>
+      </c>
+      <c r="L278">
+        <v>11.6</v>
+      </c>
+      <c r="O278">
         <v>21.7</v>
       </c>
-      <c r="L278">
+      <c r="Q278">
         <v>40.0</v>
       </c>
-      <c r="N278">
+      <c r="S278">
         <v>0</v>
       </c>
     </row>
@@ -11515,13 +14335,19 @@
       <c r="H279">
         <v>76.8</v>
       </c>
-      <c r="I279">
+      <c r="J279">
+        <v>0.0</v>
+      </c>
+      <c r="M279">
         <v>9.4</v>
       </c>
-      <c r="M279">
+      <c r="N279">
+        <v>9.4</v>
+      </c>
+      <c r="R279">
         <v>102.6</v>
       </c>
-      <c r="N279">
+      <c r="S279">
         <v>1</v>
       </c>
     </row>
@@ -11556,13 +14382,19 @@
       <c r="H280">
         <v>31.9</v>
       </c>
-      <c r="J280">
+      <c r="I280">
         <v>4.3</v>
       </c>
-      <c r="M280">
+      <c r="L280">
+        <v>0.0</v>
+      </c>
+      <c r="O280">
+        <v>4.3</v>
+      </c>
+      <c r="R280">
         <v>47.8</v>
       </c>
-      <c r="N280">
+      <c r="S280">
         <v>1</v>
       </c>
     </row>
@@ -11597,16 +14429,25 @@
       <c r="H281">
         <v>21.7</v>
       </c>
-      <c r="J281">
+      <c r="I281">
         <v>50.0</v>
       </c>
+      <c r="K281">
+        <v>25.0</v>
+      </c>
       <c r="L281">
-        <v>25.0</v>
-      </c>
-      <c r="M281">
+        <v>0.0</v>
+      </c>
+      <c r="O281">
+        <v>50.0</v>
+      </c>
+      <c r="Q281">
+        <v>25.0</v>
+      </c>
+      <c r="R281">
         <v>49.2</v>
       </c>
-      <c r="N281">
+      <c r="S281">
         <v>1</v>
       </c>
     </row>
@@ -11641,13 +14482,22 @@
       <c r="H282">
         <v>10.1</v>
       </c>
-      <c r="J282">
+      <c r="I282">
         <v>24.2</v>
       </c>
+      <c r="K282">
+        <v>25.0</v>
+      </c>
       <c r="L282">
-        <v>25.0</v>
-      </c>
-      <c r="N282">
+        <v>0.0</v>
+      </c>
+      <c r="O282">
+        <v>24.2</v>
+      </c>
+      <c r="Q282">
+        <v>25.0</v>
+      </c>
+      <c r="S282">
         <v>0</v>
       </c>
     </row>
@@ -11682,16 +14532,25 @@
       <c r="H283">
         <v>10.1</v>
       </c>
-      <c r="J283">
+      <c r="I283">
         <v>35.5</v>
       </c>
+      <c r="K283">
+        <v>25.0</v>
+      </c>
       <c r="L283">
-        <v>25.0</v>
-      </c>
-      <c r="M283">
+        <v>0.0</v>
+      </c>
+      <c r="O283">
+        <v>35.5</v>
+      </c>
+      <c r="Q283">
+        <v>25.0</v>
+      </c>
+      <c r="R283">
         <v>39.6</v>
       </c>
-      <c r="N283">
+      <c r="S283">
         <v>1</v>
       </c>
     </row>
@@ -11727,15 +14586,27 @@
         <v>48.5</v>
       </c>
       <c r="I284">
+        <v>2.9</v>
+      </c>
+      <c r="J284">
+        <v>0.0</v>
+      </c>
+      <c r="L284">
+        <v>0.0</v>
+      </c>
+      <c r="M284">
         <v>6.1</v>
       </c>
-      <c r="J284">
+      <c r="N284">
+        <v>6.1</v>
+      </c>
+      <c r="O284">
         <v>2.9</v>
       </c>
-      <c r="M284">
+      <c r="R284">
         <v>37.2</v>
       </c>
-      <c r="N284">
+      <c r="S284">
         <v>1</v>
       </c>
     </row>
@@ -11770,13 +14641,19 @@
       <c r="H285">
         <v>0.0</v>
       </c>
-      <c r="J285">
+      <c r="I285">
+        <v>0.0</v>
+      </c>
+      <c r="L285">
         <v>98.5</v>
       </c>
-      <c r="L285">
+      <c r="O285">
+        <v>98.5</v>
+      </c>
+      <c r="Q285">
         <v>20.0</v>
       </c>
-      <c r="N285">
+      <c r="S285">
         <v>0</v>
       </c>
     </row>
@@ -11811,10 +14688,16 @@
       <c r="H286">
         <v>0.0</v>
       </c>
-      <c r="J286">
+      <c r="I286">
+        <v>0.0</v>
+      </c>
+      <c r="L286">
         <v>7.7</v>
       </c>
-      <c r="N286">
+      <c r="O286">
+        <v>7.7</v>
+      </c>
+      <c r="S286">
         <v>0</v>
       </c>
     </row>
@@ -11849,16 +14732,25 @@
       <c r="H287">
         <v>23.1</v>
       </c>
-      <c r="J287">
+      <c r="I287">
         <v>32.0</v>
       </c>
+      <c r="K287">
+        <v>25.0</v>
+      </c>
       <c r="L287">
-        <v>25.0</v>
-      </c>
-      <c r="M287">
+        <v>0.0</v>
+      </c>
+      <c r="O287">
+        <v>32.0</v>
+      </c>
+      <c r="Q287">
+        <v>25.0</v>
+      </c>
+      <c r="R287">
         <v>24.3</v>
       </c>
-      <c r="N287">
+      <c r="S287">
         <v>1</v>
       </c>
     </row>
@@ -11893,16 +14785,25 @@
       <c r="H288">
         <v>24.6</v>
       </c>
-      <c r="J288">
+      <c r="I288">
         <v>44.9</v>
       </c>
+      <c r="K288">
+        <v>30.0</v>
+      </c>
       <c r="L288">
+        <v>0.0</v>
+      </c>
+      <c r="O288">
+        <v>44.9</v>
+      </c>
+      <c r="Q288">
         <v>30.0</v>
       </c>
-      <c r="M288">
+      <c r="R288">
         <v>53.6</v>
       </c>
-      <c r="N288">
+      <c r="S288">
         <v>1</v>
       </c>
     </row>
@@ -11937,16 +14838,25 @@
       <c r="H289">
         <v>12.5</v>
       </c>
-      <c r="J289">
+      <c r="I289">
         <v>21.4</v>
       </c>
+      <c r="K289">
+        <v>25.0</v>
+      </c>
       <c r="L289">
-        <v>25.0</v>
-      </c>
-      <c r="M289">
+        <v>0.0</v>
+      </c>
+      <c r="O289">
+        <v>21.4</v>
+      </c>
+      <c r="Q289">
+        <v>25.0</v>
+      </c>
+      <c r="R289">
         <v>44.4</v>
       </c>
-      <c r="N289">
+      <c r="S289">
         <v>1</v>
       </c>
     </row>
@@ -11981,16 +14891,25 @@
       <c r="H290">
         <v>17.2</v>
       </c>
-      <c r="J290">
+      <c r="I290">
         <v>60.4</v>
       </c>
+      <c r="K290">
+        <v>35.0</v>
+      </c>
       <c r="L290">
+        <v>0.0</v>
+      </c>
+      <c r="O290">
+        <v>60.4</v>
+      </c>
+      <c r="Q290">
         <v>35.0</v>
       </c>
-      <c r="M290">
+      <c r="R290">
         <v>77.8</v>
       </c>
-      <c r="N290">
+      <c r="S290">
         <v>1</v>
       </c>
     </row>
@@ -12025,13 +14944,19 @@
       <c r="H291">
         <v>82.5</v>
       </c>
-      <c r="I291">
+      <c r="J291">
+        <v>0.0</v>
+      </c>
+      <c r="M291">
         <v>5.8</v>
       </c>
-      <c r="M291">
+      <c r="N291">
+        <v>5.8</v>
+      </c>
+      <c r="R291">
         <v>86.9</v>
       </c>
-      <c r="N291">
+      <c r="S291">
         <v>1</v>
       </c>
     </row>
@@ -12066,16 +14991,25 @@
       <c r="H292">
         <v>12.7</v>
       </c>
-      <c r="J292">
+      <c r="I292">
+        <v>27.3</v>
+      </c>
+      <c r="K292">
+        <v>25.0</v>
+      </c>
+      <c r="L292">
+        <v>1.8</v>
+      </c>
+      <c r="O292">
         <v>29.1</v>
       </c>
-      <c r="L292">
-        <v>25.0</v>
-      </c>
-      <c r="M292">
+      <c r="Q292">
+        <v>25.0</v>
+      </c>
+      <c r="R292">
         <v>46.9</v>
       </c>
-      <c r="N292">
+      <c r="S292">
         <v>1</v>
       </c>
     </row>
@@ -12110,16 +15044,25 @@
       <c r="H293">
         <v>20.6</v>
       </c>
-      <c r="J293">
+      <c r="I293">
         <v>24.0</v>
       </c>
+      <c r="K293">
+        <v>20.0</v>
+      </c>
       <c r="L293">
+        <v>0.0</v>
+      </c>
+      <c r="O293">
+        <v>24.0</v>
+      </c>
+      <c r="Q293">
         <v>20.0</v>
       </c>
-      <c r="M293">
+      <c r="R293">
         <v>70.3</v>
       </c>
-      <c r="N293">
+      <c r="S293">
         <v>1</v>
       </c>
     </row>
@@ -12154,16 +15097,25 @@
       <c r="H294">
         <v>21.0</v>
       </c>
-      <c r="J294">
+      <c r="I294">
+        <v>28.6</v>
+      </c>
+      <c r="K294">
+        <v>25.0</v>
+      </c>
+      <c r="L294">
+        <v>8.2</v>
+      </c>
+      <c r="O294">
         <v>36.7</v>
       </c>
-      <c r="L294">
-        <v>25.0</v>
-      </c>
-      <c r="M294">
+      <c r="Q294">
+        <v>25.0</v>
+      </c>
+      <c r="R294">
         <v>63.2</v>
       </c>
-      <c r="N294">
+      <c r="S294">
         <v>1</v>
       </c>
     </row>
@@ -12198,10 +15150,16 @@
       <c r="H295">
         <v>0.0</v>
       </c>
-      <c r="J295">
+      <c r="I295">
         <v>1.6</v>
       </c>
-      <c r="N295">
+      <c r="L295">
+        <v>0.0</v>
+      </c>
+      <c r="O295">
+        <v>1.6</v>
+      </c>
+      <c r="S295">
         <v>0</v>
       </c>
     </row>
@@ -12236,10 +15194,16 @@
       <c r="H296">
         <v>0.0</v>
       </c>
-      <c r="J296">
+      <c r="I296">
         <v>11.3</v>
       </c>
-      <c r="N296">
+      <c r="L296">
+        <v>0.0</v>
+      </c>
+      <c r="O296">
+        <v>11.3</v>
+      </c>
+      <c r="S296">
         <v>0</v>
       </c>
     </row>
@@ -12274,19 +15238,28 @@
       <c r="H297">
         <v>53.2</v>
       </c>
-      <c r="I297">
-        <v>60.6</v>
+      <c r="J297">
+        <v>0.0</v>
       </c>
       <c r="K297">
         <v>10.0</v>
       </c>
-      <c r="L297">
+      <c r="M297">
+        <v>60.6</v>
+      </c>
+      <c r="N297">
+        <v>60.6</v>
+      </c>
+      <c r="P297">
         <v>10.0</v>
       </c>
-      <c r="M297">
+      <c r="Q297">
+        <v>10.0</v>
+      </c>
+      <c r="R297">
         <v>62.9</v>
       </c>
-      <c r="N297">
+      <c r="S297">
         <v>1</v>
       </c>
     </row>
@@ -12321,16 +15294,25 @@
       <c r="H298">
         <v>32.3</v>
       </c>
-      <c r="J298">
+      <c r="I298">
         <v>35.7</v>
       </c>
+      <c r="K298">
+        <v>25.0</v>
+      </c>
       <c r="L298">
-        <v>25.0</v>
-      </c>
-      <c r="M298">
+        <v>0.0</v>
+      </c>
+      <c r="O298">
+        <v>35.7</v>
+      </c>
+      <c r="Q298">
+        <v>25.0</v>
+      </c>
+      <c r="R298">
         <v>58.1</v>
       </c>
-      <c r="N298">
+      <c r="S298">
         <v>1</v>
       </c>
     </row>
@@ -12365,13 +15347,19 @@
       <c r="H299">
         <v>0.0</v>
       </c>
-      <c r="J299">
+      <c r="I299">
+        <v>11.5</v>
+      </c>
+      <c r="L299">
+        <v>23.0</v>
+      </c>
+      <c r="O299">
         <v>34.4</v>
       </c>
-      <c r="L299">
+      <c r="Q299">
         <v>35.0</v>
       </c>
-      <c r="N299">
+      <c r="S299">
         <v>0</v>
       </c>
     </row>
@@ -12406,10 +15394,16 @@
       <c r="H300">
         <v>26.2</v>
       </c>
-      <c r="J300">
+      <c r="I300">
+        <v>0.0</v>
+      </c>
+      <c r="L300">
         <v>20.0</v>
       </c>
-      <c r="N300">
+      <c r="O300">
+        <v>20.0</v>
+      </c>
+      <c r="S300">
         <v>0</v>
       </c>
     </row>
@@ -12444,20 +15438,29 @@
       <c r="H301">
         <v>15.0</v>
       </c>
-      <c r="J301">
+      <c r="I301">
         <v>82.4</v>
       </c>
+      <c r="K301">
+        <v>40.0</v>
+      </c>
       <c r="L301">
+        <v>0.0</v>
+      </c>
+      <c r="O301">
+        <v>82.4</v>
+      </c>
+      <c r="Q301">
         <v>40.0</v>
       </c>
-      <c r="M301">
+      <c r="R301">
         <v>33.9</v>
       </c>
-      <c r="N301">
+      <c r="S301">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N301"/>
+  <autoFilter ref="A1:S301"/>
 </worksheet>
 </file>